--- a/02_Glider_Design/C_results/nausicaa_workflow.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_workflow.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5cb9697-dirty</t>
+          <t>b5c9594-dirty</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-22T00:00:06.852190+00:00</t>
+          <t>2026-02-22T21:59:16.557802+00:00</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03224942917054652</v>
+        <v>0.03224942926190789</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6294856307726406</v>
+        <v>0.6294856343110077</v>
       </c>
     </row>
     <row r="4">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.340197586387651e-07</v>
+        <v>8.340161805147485e-07</v>
       </c>
     </row>
     <row r="5">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001820511558746352</v>
+        <v>-0.001820511524613933</v>
       </c>
     </row>
     <row r="6">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.07529548797726575</v>
+        <v>-0.07529549634031213</v>
       </c>
     </row>
     <row r="7">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.380160661236591e-05</v>
+        <v>-8.380160268495196e-05</v>
       </c>
     </row>
     <row r="8">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.005053025496728</v>
+        <v>7.005053156532401</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.890867534687543e-05</v>
+        <v>-2.890875486074246e-05</v>
       </c>
     </row>
     <row r="11">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01586307811807242</v>
+        <v>-0.01586307786877184</v>
       </c>
     </row>
     <row r="12">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3676832465103752</v>
+        <v>0.3676832720721501</v>
       </c>
     </row>
     <row r="13">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0001684725206008153</v>
+        <v>-0.0001684725177697466</v>
       </c>
     </row>
     <row r="14">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.422363200144823e-18</v>
+        <v>-1.14709254935964e-17</v>
       </c>
     </row>
     <row r="15">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-7.075447656711423e-23</v>
+        <v>-1.811288389569231e-13</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3099907511324865</v>
+        <v>-0.3099907611852864</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.566406099598727</v>
+        <v>-0.5664061109614236</v>
       </c>
     </row>
     <row r="18">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2.441226992436795e-18</v>
+        <v>4.920359370436785e-15</v>
       </c>
     </row>
     <row r="19">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1241092086103912</v>
+        <v>0.1241092089572653</v>
       </c>
     </row>
     <row r="20">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.087405529260732e-19</v>
+        <v>-1.238244227167802e-18</v>
       </c>
     </row>
     <row r="21">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.33346092137015e-19</v>
+        <v>-1.956947532065448e-13</v>
       </c>
     </row>
     <row r="22">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2819421253289612</v>
+        <v>-0.2819421310024662</v>
       </c>
     </row>
     <row r="23">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.064729109304657</v>
+        <v>-1.064729130000453</v>
       </c>
     </row>
     <row r="24">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.711870338836074e-18</v>
+        <v>5.11993665936314e-15</v>
       </c>
     </row>
     <row r="25">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.021790251455553</v>
+        <v>0.02179025168256403</v>
       </c>
     </row>
     <row r="26">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.491448830018954e-10</v>
+        <v>-2.043139912434701e-10</v>
       </c>
     </row>
     <row r="27">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3502525826742454</v>
+        <v>-0.3502525891591913</v>
       </c>
     </row>
     <row r="28">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.002744686737054e-05</v>
+        <v>-1.002756527529876e-05</v>
       </c>
     </row>
     <row r="29">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.006396571209649135</v>
+        <v>-0.006396570981524612</v>
       </c>
     </row>
     <row r="30">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-39.52415518558014</v>
+        <v>-39.52415465967306</v>
       </c>
     </row>
     <row r="31">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001389555989351931</v>
+        <v>-0.0001389555864853396</v>
       </c>
     </row>
     <row r="32">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.05887327666648e-18</v>
+        <v>5.177796536276711e-18</v>
       </c>
     </row>
     <row r="33">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-7.578978318717902e-21</v>
+        <v>-1.528864420935966e-14</v>
       </c>
     </row>
     <row r="34">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03795793197254786</v>
+        <v>0.03795793239845403</v>
       </c>
     </row>
     <row r="35">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.07056892499093069</v>
+        <v>-0.07056892371846811</v>
       </c>
     </row>
     <row r="36">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.725461716079436e-19</v>
+        <v>3.586475024903658e-16</v>
       </c>
     </row>
     <row r="37">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05850484150544907</v>
+        <v>-0.05850483910941145</v>
       </c>
     </row>
     <row r="38">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.07963424090427679</v>
+        <v>0.07963423851923263</v>
       </c>
     </row>
     <row r="39">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01223295076335761</v>
+        <v>0.01223295000408741</v>
       </c>
     </row>
     <row r="40">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06740129014091917</v>
+        <v>0.06740128851514521</v>
       </c>
     </row>
     <row r="41">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02972920125926148</v>
+        <v>-0.02972920083507641</v>
       </c>
     </row>
     <row r="42">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02972920125926148</v>
+        <v>0.02972920083507641</v>
       </c>
     </row>
     <row r="43">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.07963424090427679</v>
+        <v>-0.07963423851923263</v>
       </c>
     </row>
     <row r="44">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8737940869410059</v>
+        <v>0.873794058170949</v>
       </c>
     </row>
     <row r="45">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.254464203857359e-18</v>
+        <v>-5.031192021622866e-18</v>
       </c>
     </row>
     <row r="46">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.254464203857359e-18</v>
+        <v>5.031192021622866e-18</v>
       </c>
     </row>
     <row r="47">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.129665040971596e-19</v>
+        <v>-3.824577332181577e-18</v>
       </c>
     </row>
     <row r="48">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.326685340691906e-17</v>
+        <v>-2.832541343211853e-17</v>
       </c>
     </row>
     <row r="49">
@@ -1160,11 +1160,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00019699568249745332,
+	L=0.00019699567303608487,
 	Y=0.0,
-	D=0.0008275962517129193,
+	D=0.0008275962274152107,
 	l_b=-0.0,
-	m_b=-8.809874262680897e-05,
+	m_b=-8.809873553677019e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.254464203857359e-18</v>
+        <v>-5.031192021622866e-18</v>
       </c>
     </row>
     <row r="51">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-5.639640543572601e-11</v>
+        <v>-7.725758810364462e-11</v>
       </c>
     </row>
     <row r="52">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.649187703175008e-17</v>
+        <v>2.103824758584693e-17</v>
       </c>
     </row>
     <row r="53">
@@ -1210,29 +1210,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.783353256168381,
+	L=0.7833532308652463,
+	Y=-1.734723475976807e-18,
+	D=0.05625017879996465,
+	l_b=-3.469446951953614e-18,
+	m_b=0.06668582602977607,
+	n_b=-5.421010862427522e-20,
+	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+), AeroComponentResults(
+	L=0.09024383163266649,
 	Y=0.0,
-	D=0.05625018019951093,
+	D=0.007883984453949123,
 	l_b=-0.0,
-	m_b=0.06668583167694779,
+	m_b=-0.06663054190862432,
 	n_b=-0.0,
-	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
-), AeroComponentResults(
-	L=0.09024383509012739,
-	Y=0.0,
-	D=0.007883984678618852,
-	l_b=-0.0,
-	m_b=-0.06663054752102311,
-	n_b=-0.0,
-	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=-0.0,
-	Y=2.326685340691906e-17,
-	D=0.0024395290110764732,
-	l_b=1.2544642038573592e-18,
-	m_b=3.2814530305724925e-05,
-	n_b=-1.6491877031750078e-17,
-	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
+	Y=-2.6590689956141722e-17,
+	D=0.0024395290338162295,
+	l_b=-1.5617450696692519e-18,
+	m_b=3.2814537127424117e-05,
+	n_b=2.10924576944712e-17,
+	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1282692273998176</v>
+        <v>0.1282692216227911</v>
       </c>
     </row>
     <row r="55">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3220966530276053</v>
+        <v>0.3220966430871982</v>
       </c>
     </row>
     <row r="56">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.03434113097875773</v>
+        <v>0.03329226774080776</v>
       </c>
     </row>
     <row r="57">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
     </row>
     <row r="58">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.884426405928886e-17</v>
+        <v>-2.835765446046807e-17</v>
       </c>
     </row>
     <row r="59">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6.402903091352355e-19</v>
+        <v>-6.38219382057322e-18</v>
       </c>
     </row>
     <row r="60">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.01094067023361572</v>
+        <v>0.005146727224944566</v>
       </c>
     </row>
     <row r="61">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-8.517569654817715e-18</v>
+        <v>1.045481716114787e-17</v>
       </c>
     </row>
     <row r="62">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.04769962156816282</v>
+        <v>0.06294152819570649</v>
       </c>
     </row>
     <row r="63">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.006840332530788545</v>
+        <v>0.009382912642914253</v>
       </c>
     </row>
     <row r="64">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.04085928903737427</v>
+        <v>0.05355861555279223</v>
       </c>
     </row>
     <row r="65">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.01970625031065464</v>
+        <v>-0.02469508896185747</v>
       </c>
     </row>
     <row r="66">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.01970625031065464</v>
+        <v>0.02469508896185747</v>
       </c>
     </row>
     <row r="67">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.04769962156816282</v>
+        <v>-0.06294152819570649</v>
       </c>
     </row>
     <row r="68">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4900533454460951</v>
+        <v>0.6696076031664475</v>
       </c>
     </row>
     <row r="69">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.463403371267119e-18</v>
+        <v>-1.985412154532852e-17</v>
       </c>
     </row>
     <row r="70">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.463403371267119e-18</v>
+        <v>1.985412154532852e-17</v>
       </c>
     </row>
     <row r="71">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3.520786789153028e-19</v>
+        <v>-1.796917958637743e-17</v>
       </c>
     </row>
     <row r="72">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.617456789395252e-17</v>
+        <v>-5.361227182490354e-17</v>
       </c>
     </row>
     <row r="73">
@@ -1436,11 +1436,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00011968880593709713,
+	L=0.00015610787456671668,
 	Y=0.0,
-	D=0.0004967411139152521,
+	D=0.0006528172936150688,
 	l_b=-0.0,
-	m_b=-5.357034034996522e-05,
+	m_b=-6.98681858411693e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.463403371267119e-18</v>
+        <v>-1.985412154532852e-17</v>
       </c>
     </row>
     <row r="75">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.00232707039471125</v>
+        <v>0.001490013816381656</v>
       </c>
     </row>
     <row r="76">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.946716976662864e-17</v>
+        <v>3.252348902073505e-17</v>
       </c>
     </row>
     <row r="77">
@@ -1486,29 +1486,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.4422075354169336,
+	L=0.6021268984154694,
+	Y=-7.806255641895632e-18,
+	D=0.0447321314774594,
+	l_b=-1.734723475976807e-17,
+	m_b=0.05125661033137777,
+	n_b=-5.963111948670274e-19,
+	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+), AeroComponentResults(
+	L=0.06732459687641117,
 	Y=0.0,
-	D=0.03410682128253058,
+	D=0.006156568354581533,
 	l_b=-0.0,
-	m_b=0.03762132831443529,
+	m_b=-0.04972386067737028,
 	n_b=-0.0,
-	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
-), AeroComponentResults(
-	L=0.04772612122322445,
-	Y=0.0,
-	D=0.0046365157976351636,
-	l_b=-0.0,
-	m_b=-0.03526246786689981,
-	n_b=-0.0,
-	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=1.3552527156068805e-20,
-	Y=2.6174567893952522e-17,
-	D=0.0016192108432932818,
-	l_b=1.4634033712671194e-18,
-	m_b=2.1780287525730196e-05,
-	n_b=-1.9467169766628638e-17,
-	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
+	Y=-4.5806016183007906e-17,
+	D=0.0020170984271362254,
+	l_b=-2.5068867855604483e-18,
+	m_b=2.713234821533858e-05,
+	n_b=3.311980021560208e-17,
+	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8737940869410059</v>
+        <v>0.873794058170949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8737940969317202</v>
+        <v>0.8737940681678181</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07963424090427679</v>
+        <v>0.07963423851923263</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.491448830018954e-10</v>
+        <v>-2.043139912434701e-10</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.087405529260732e-19</v>
+        <v>-1.238244227167802e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4.05887327666648e-18</v>
+        <v>5.177796536276711e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.97259265635919</v>
+        <v>10.97259262371068</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41933.23691995171</v>
+        <v>41933.23557384799</v>
       </c>
       <c r="C14" t="n">
         <v>20000</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C15" t="n">
         <v>0.05</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C17" t="n">
         <v>0.5</v>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C19" t="n">
         <v>0.03</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2819421253289612</v>
+        <v>-0.2819421310024662</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03795793197254786</v>
+        <v>0.03795793239845403</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-39.52415518558014</v>
+        <v>-39.52415465967306</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5999999902481539</v>
+        <v>0.5999999902182078</v>
       </c>
       <c r="C24" t="n">
         <v>0.6</v>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64.60823526290454</v>
+        <v>64.60823651215563</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.009286741663916792</v>
+        <v>0.009286741483886836</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.761185342964752e-06</v>
+        <v>7.761184839387542e-06</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.628272149107434e-07</v>
+        <v>1.628272027785878e-07</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.358258982162884e-22</v>
+        <v>5.05083796544096e-22</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>1.086407042169356e-15</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3645446504338175</v>
+        <v>0.3645446515159374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.769816175392</v>
+        <v>1.047805349839111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,70 +2757,70 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3829646626678594</v>
+        <v>0.3829646626598319</v>
       </c>
       <c r="C2" t="n">
-        <v>1.645457929412684</v>
+        <v>1.645457928290766</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1531317527442298</v>
+        <v>0.1531317478285296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8367187539795161</v>
+        <v>0.8367187148415608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3593336687022275</v>
+        <v>0.3593336654808725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1711121863070972</v>
+        <v>0.1711121874275478</v>
       </c>
       <c r="H2" t="n">
-        <v>10.74537383609153</v>
+        <v>10.74537417370354</v>
       </c>
       <c r="I2" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="J2" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="L2" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3645446504338175</v>
+        <v>0.3645446515159374</v>
       </c>
       <c r="N2" t="n">
-        <v>10.97259265635919</v>
+        <v>10.97259262371068</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08907177338753518</v>
+        <v>0.08907177045543507</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001248044074387546</v>
+        <v>0.001248042840409447</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009286741663916792</v>
+        <v>0.009286741483886836</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5999999902481539</v>
+        <v>0.5999999902182078</v>
       </c>
       <c r="V2" t="n">
-        <v>64.60823526290454</v>
+        <v>64.60823651215563</v>
       </c>
       <c r="W2" t="n">
-        <v>5.389712043725522e-05</v>
+        <v>5.389711694019127e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2834,7 +2834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2955,58 +2955,58 @@
         <v>0.9523224268498633</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03770708887131363</v>
+        <v>0.02423393716631873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.400402103862616</v>
+        <v>-0.2379819250052098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.756370322009981</v>
+        <v>0.9831732299281261</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06874234197651</v>
+        <v>1.222883288467837</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.658634349602988</v>
+        <v>3.304322906408986</v>
       </c>
       <c r="J2" t="n">
-        <v>9.989615409202111e-17</v>
+        <v>4.476784574344764e-12</v>
       </c>
       <c r="K2" t="n">
-        <v>1.34561812479422</v>
+        <v>0.9553718353333818</v>
       </c>
       <c r="L2" t="n">
-        <v>1.036128223452248e-15</v>
+        <v>-2.751677478147776e-14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3893668859295748</v>
+        <v>0.4455336575479304</v>
       </c>
       <c r="N2" t="n">
-        <v>10.27308714699075</v>
+        <v>8.977997249494749</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3318690554554731</v>
+        <v>0.331869055469902</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08100132831746366</v>
+        <v>0.0926858913473748</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.341365650397012</v>
+        <v>8.695677093591014</v>
       </c>
       <c r="R2" t="n">
-        <v>0.718130944544527</v>
+        <v>0.7181309445300981</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04485393749314066</v>
+        <v>0.03184572784444606</v>
       </c>
       <c r="T2" t="n">
-        <v>3.453760744840826e-17</v>
+        <v>9.172258260492586e-16</v>
       </c>
       <c r="U2" t="n">
-        <v>3.32987180306737e-18</v>
+        <v>1.492261524781588e-13</v>
       </c>
     </row>
     <row r="3">
@@ -3020,58 +3020,3178 @@
         <v>0.9596982286828247</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04897008694378837</v>
+        <v>-0.005228325494213273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9142421072471785</v>
+        <v>-0.7907865347605347</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7165439881999204</v>
+        <v>0.77339802870779</v>
       </c>
       <c r="G3" t="n">
-        <v>1.164358253718898</v>
+        <v>1.060851969750053</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.212684409844941</v>
+        <v>3.893532139456988</v>
       </c>
       <c r="J3" t="n">
-        <v>2.243596228336229e-14</v>
+        <v>1.140347043572175e-16</v>
       </c>
       <c r="K3" t="n">
-        <v>0.695722859086041</v>
+        <v>0.9886287002693678</v>
       </c>
       <c r="L3" t="n">
-        <v>1.13524117002072e-15</v>
+        <v>3.856632831908949e-15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4243064442276523</v>
+        <v>0.3863368240727492</v>
       </c>
       <c r="N3" t="n">
-        <v>9.427148719562824</v>
+        <v>10.35365956122035</v>
       </c>
       <c r="O3" t="n">
-        <v>0.334439403906574</v>
+        <v>0.3344394038620549</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08895358098469723</v>
+        <v>0.08099345014381293</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.78731559015506</v>
+        <v>8.106467860543011</v>
       </c>
       <c r="R3" t="n">
-        <v>0.715560596093426</v>
+        <v>0.7155605961379452</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0231907619695347</v>
+        <v>0.03295429000897893</v>
       </c>
       <c r="T3" t="n">
-        <v>3.784137233402401e-17</v>
+        <v>1.285544277302983e-16</v>
       </c>
       <c r="U3" t="n">
-        <v>7.478654094454096e-16</v>
+        <v>3.80115681190725e-18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.062845148118856</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04772809765118106</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4533107059615955</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8922345578505793</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.117081095464179</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.910958637724466</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3.476932991341167e-14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.206986261638216</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.274237816005903e-15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4058485890528634</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.855892233977958</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3703844474440711</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.09422868612806551</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9.089041362275534</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6796155525559289</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04023287538794052</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.424745938668634e-16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.158977663780389e-15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9183831884270194</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04022198456307356</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.8582695778428184</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8080292598298258</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.088762361760061</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.824378932071722</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-3.974778579704026e-13</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.273012516216683</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.274147966697914e-14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3981398784071271</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10.04672017852401</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3200417763731435</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.07987460167256902</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.175621067928278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7299582236268566</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0424337505405561</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.247159888993045e-16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.324926193234675e-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.020020105193131</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01378858386230201</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.63853204033768</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9091970033516752</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.047595221719247</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.639862909378391</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.796872811365531e-14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7669298924632399</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.510214134872906e-14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.380555630316454</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10.51094672257747</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3554606082965004</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.08479612073764514</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10.36013709062161</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.6945393917034997</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02556432974877466</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.034047116243021e-16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.322909371218436e-16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.045712105362359</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05684145236462675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.847479832792306</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7260748300443259</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.118412867085656</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.46122537693976</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9.74660478238093e-17</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.564424936631776</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.010912165366173e-15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4061386460479052</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.848853318191001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.364413857002689</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.09277598052687698</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10.53877462306024</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.685586142997311</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.05214749788772585</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.369707217887245e-17</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.248868260793643e-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9375802146733208</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01104744132940376</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.76226053825639</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.840989764061928</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.045407581752856</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.795458565667494</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.286159331159278e-13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.025684796372473</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.674027821033227e-16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3814450938072939</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.48643701632289</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3267316314825974</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.07812491686003664</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.204541434332506</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.7232683685174026</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.03418949321241578</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8.913426070110756e-18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.287197770530926e-15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9110293254666136</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03190599770583577</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.163761123380084</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8765472411070281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.199751872914643</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.11443557562578</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.20249497041105e-12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.118942002873559</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3.317667387578575e-15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4391606001702414</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.108285090896258</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3174790731028429</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.08739867077453634</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.88556442437422</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7325209268971571</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.03729806676245197</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.105889129192858e-16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.008316568036835e-14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9549938735812077</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.01113667698244716</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2520927330236313</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8879427207774048</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.153705410406969</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.840871847317237</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.265654081707218e-12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8221104106184941</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.078995578505928e-15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4203400914384868</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.516103822232424</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3328000116037095</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08769008695062748</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9.159128152682763</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7171999883962905</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0274036803539498</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.596651928353092e-17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.218846939024061e-14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.031486602975119</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.03645961056380737</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.082640917935918</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9078386422514689</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.070782688208963</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.243273274602304</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.17493919648789e-14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6039127504191784</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.756558955355853e-15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3891529965250833</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.27873353522959</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3594564984757814</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.08768656780594906</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.756726725397696</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6905435015242187</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.02013042501397261</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.252186318451951e-16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.916463988292968e-16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.012453132556086</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.03938675819017985</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.743903074702475</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9674144119003019</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.243276248816004</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.015922882335473</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.293507605490501e-16</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5564875926661516</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.927358624678597e-15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.4518957282649883</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.851599394860926</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3528236399492594</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.09994527452896465</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.984077117664527</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.6971763600507407</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01854958642220505</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.309119541559532e-16</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.311692018301669e-18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9300124526610672</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.03825525285228158</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.260789262280481</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7723750629722278</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.086319211117186</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.299366566873276</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.186253435711402e-16</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7405250036535284</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.860181016303757e-15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3969114026373693</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10.07781565746276</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3240943878220154</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.08063645749628615</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.700633433126724</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.7259056121779847</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.02468416678845094</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.286727005434586e-16</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.28751145237134e-18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9865261581609575</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.01245666207149262</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1731195132372432</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7459582951999558</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.167814165299733</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.340623692883124</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.89368818515174e-16</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.162392223171917</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.852959968847916e-15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.424497007294537</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.422916733079829</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3437885060449258</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.09148130238452208</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.659376307116876</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7062114939550742</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.03874640743906391</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.284319989615972e-16</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63122939505058e-17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.033859459714904</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0464840573866418</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6747630342006934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8171820811638927</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.183305931621063</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.664461627162652</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-4.089195645645791e-17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5901014746344447</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.865357751324869e-15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4301626703433465</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.298807710539954</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.3602834009076397</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.09715011659033988</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9.335538372837348</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6897165990923604</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01967004915448149</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.288452583774956e-16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.363065215215264e-18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9845569346540256</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.05761071013950942</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.613311707955246</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8706484443067354</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.06630659754416</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.589023443142051</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.892769484571283e-14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4994215765304709</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.536958719134239e-15</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3880553265436852</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.30780839748446</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3431022633506022</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.08346100025610662</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10.41097655685795</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.7068977366493978</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01664738588434903</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.178986239711413e-16</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.964256494857094e-15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.026636879854823</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03995963570261046</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.467891854166201</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9881586282761664</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.002940950396953</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.796651136320023</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-6.633415983770086e-13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.043449469318529</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.51082005030593e-15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3641445750762806</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.98464793726109</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3577664479132223</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.08166572209850607</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10.20334886367998</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6922335520867777</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.03478164897728431</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5.036066834353099e-17</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.211138661256695e-14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.093487190498735</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.0480706658480831</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.175021661673031</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9131516756849255</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.223153969158284</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.346667758780617</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.09894263004729e-14</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4747823213901237</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-7.906938946516838e-14</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4460046170168129</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.968516929348034</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3810627067216965</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1065374150751256</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.653332241219383</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6689372932783035</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.01582607737967079</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.635646315505613e-15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.996475433490967e-16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.036612964461925</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.005929855733788542</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.789071426493796</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9215327652008887</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.239104128397907</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.110889061361647</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-4.082126377851675e-12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8042862451176097</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-4.478752507989646e-12</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4500840583074406</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.887228690057103</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3612429530590923</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1019199888898929</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.889110938638353</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.6887570469409077</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.02680954150392032</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.492917502663216e-13</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.360708792617225e-13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9783249666160053</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.001380171229923677</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.90654597316875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9918151161431872</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.042557020854498</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.245903489017549</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.640606097098242e-16</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.7911820103215991</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.929733955849696e-15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3791769686036562</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.54916381344972</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3409305228874782</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.08103528946008864</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10.75409651098245</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.7090694771125219</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.02637273367738664</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.309911318616565e-16</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8.802020323660806e-18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9374505139440197</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01443268900602748</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4585117966046273</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7803229488275769</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.038401302780963</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.572535697637323</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-9.53896881553969e-15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.130658859170102</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.91234013790437e-15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3788870472172531</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10.55723593790041</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3266864328547442</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.07759026066366187</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9.427464302362678</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.7233135671452557</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.03768862863900339</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.304113379301457e-16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.179656271846563e-16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9691921331143467</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0004817378881915926</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.6555367391942</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7778384876577633</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.108166854860849</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.781461162747518</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.487322819202191e-15</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.025157882589189</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.608868889918738e-15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4032630889373812</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.919082759691623</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.3377478769832202</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.08537829025298875</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.218538837252482</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7122521230167799</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.03417192941963963</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8.696229633062461e-17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.495774273067397e-16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.002213194713915</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05248117724747617</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.9802848984409387</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8267622512706706</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.149392392037435</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.16842025640733</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.122143926325577e-14</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.340269593953248</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3.775528298081806e-15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4174995603038805</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9.580848304266175</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3492551861920419</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.09140400795204888</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7.83157974359267</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.7007448138079582</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.04467565313177493</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.258509432693935e-16</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.740479754418591e-16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.078241881900116</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.03004759132359308</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4830163382651635</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7886260022259199</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.247245656839369</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.938472844849013</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.636085331529849e-15</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.216921564917714</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.840523109346078e-15</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4535105720910369</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8.820081042747164</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3757499656422727</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1068200343954391</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9.061527155150987</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.6742500343577273</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.04056405216392379</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.280174369782026e-16</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.545361777176616e-16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.055112788494538</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.008935979745955891</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.4574395324654419</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8953310155685408</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.240874029338985</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.824153980483951</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.742195631422631e-13</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9268062314453862</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.935551589953936e-15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4508156988940261</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8.87280537587324</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3676898443917073</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1039075294444745</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8.175846019516049</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6823101556082928</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.03089354104817954</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6.451838633179787e-17</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.247398543807544e-14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9636293201230749</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.014072656404634</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2135860980378315</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9855141762458608</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.246963209986492</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.316542912575991</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.60666276338432e-11</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8920059418562102</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.106017997846375e-13</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4539055253964103</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.812406390235674</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.3358093260427382</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.09554865454051327</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8.683457087424008</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7141906739572619</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.02973353139520701</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.686726659487916e-15</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.355542544614399e-13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.084843379301365</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0007861789928376231</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.218340262394999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7460534477608073</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.061392353809357</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.242867162866323</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-6.915581612303877e-11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.025866310308583</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.788975821542714e-13</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3862449921854783</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10.35612121278561</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3780504773491535</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.09153327583124631</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>9.757132837133677</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.6719495226508465</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.03419554367695276</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5.963252738475714e-15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.305193870767959e-12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9941819770831516</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.05577141706504256</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.296123909659114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8553843046660404</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.149720800447947</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.867755347396106</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.201310388648588e-13</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.317970196606084</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.284450241213097e-15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4177454437329176</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.575209054857268</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.3464564360564671</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.09072494392591375</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10.13224465260389</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.703543563943533</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.04393233988686947</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.094816747071032e-16</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.00436796216196e-15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.038751768440446</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.03280487239690359</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1871479207212308</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9032734296394711</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.108967285928433</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.157924119671752</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-5.989716655907531e-14</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.6291165570359142</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.309679691091792e-15</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4030339334137324</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9.924722522791221</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.3619882919040551</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.09145395466567424</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8.842075880328247</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.6880117080959449</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.02097055190119714</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.436559897030597e-16</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.996572218635844e-15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9214414616907176</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0226832564578282</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.169804416217779</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8479532999743397</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.05785057393447</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.813572360418553</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.854336092442527e-14</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.096078923314459</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.081499163363317e-15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3866906619643057</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10.3441855309298</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.3211075354514141</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.07783600468159958</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>10.18642763958145</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.7288924645485859</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.03653596411048198</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.027166387787772e-16</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.951445364147509e-15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9209087116865883</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.006611601467743825</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.3759802836277824</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9741231522682052</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.016344342679179</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.36624110585392</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1.095860396592616e-12</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8594352354586997</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.733977711065704e-15</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3715700558695607</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10.76512998513119</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.3209218806063773</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.07474917262052197</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8.63375889414608</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.7290781193936227</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.02864784118195666</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.244659237021901e-16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.652867988642055e-14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9403814895058901</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.05495858531175767</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.897927349273641</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9210693958604375</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.042182093439014</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.178256924396214</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-2.064045708942665e-16</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.5076544943074542</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3.583487735584002e-15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.3804751198677824</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10.51317101055291</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.3277078347433813</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.07815907936898554</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>10.82174307560379</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.7222921652566188</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.01692181647691514</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.194495911861334e-16</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6.880152363142218e-18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.076889934737659</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.02446200002595195</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4206366617041435</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9646530386831706</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.089612932196552</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.033544753789603</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.603818778682494e-16</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.6246870710482415</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.730799305354591e-15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.3965248347957794</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10.08764043655849</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.3752788298450969</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.09328048843368966</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.966455246210398</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.6747211701549032</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.02082290236827472</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.24359976845153e-16</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.201272926227498e-17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.035962292296917</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.05126003224819094</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.870791930747273</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.7335294964357321</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.022005432618789</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.41343041733767</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-3.644232809521528e-13</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.500958634038613</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.627393123722422e-17</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3710757016944433</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10.77947151390694</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.3610162042692784</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.08397607384655573</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>10.58656958266233</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.6889837957307217</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.05003195446795376</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.209131041240807e-18</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.214744269840509e-14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.069847264722887</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03414778289159998</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.824049231774412</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7587290510490128</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.037684747842489</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.217843013407529</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-4.369497988197704e-15</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.302532800968871</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.884544482893964e-15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3771323153649909</v>
+      </c>
+      <c r="N35" t="n">
+        <v>10.60635695841004</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.3728245725396315</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.08813829172917757</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6.782156986592471</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.6771754274603685</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0434177600322957</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.294848160964655e-16</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.456499329399235e-16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.028887253841104</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.05846026877635341</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.530770611370802</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.7197112676810835</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.011162871292468</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.801234693063309</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1.394618204007597e-16</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.5654613176685455</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.854906104027638e-15</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3676836466473951</v>
+      </c>
+      <c r="N36" t="n">
+        <v>10.87891722160161</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.3585506670816223</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.08264017005832525</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>10.19876530693669</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.6914493329183777</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.01884871058895151</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.284968701342546e-16</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.648727346691988e-18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9813084795351074</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.02440484044047062</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2375087501795061</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9487958495394054</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.155726568423043</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.936461498311879</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.175739702001091e-16</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.67823041887137</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3.856296786646905e-15</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.4203930801376322</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9.514904365559062</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3419702289502701</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.09011772326226393</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9.063538501688122</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.7080297710497299</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.02260768062904567</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.285432262215635e-16</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.05857990066703e-17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.003315638824999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.05882335811441234</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8545561238351889</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9888455985417449</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.123179119966526</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.402613153865445</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.644612368862027e-14</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.4230514717788211</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.845491877831403e-15</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.4084997373249968</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9.791927849617847</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.3496393702503878</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.08953203671343322</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>9.597386846134555</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.7003606297496122</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0141017157259607</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.281830625943801e-16</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.214870789620676e-15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.018688703551181</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.03929603315736935</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.22962009848392</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.7041973063085301</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.060888250774974</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.47195402831268</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-9.963546988317679e-13</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.459143048335486</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.170646571444568e-14</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.3852075702469087</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10.38401180037359</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3549966362111778</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.08572063992020219</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.52804597168732</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.6950033637888222</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.04863810161118288</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.056882190481523e-15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3.321182329439227e-14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.072423596981526</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.04675588892291244</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1947655039639726</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9367760931614727</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.131587184880575</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.260847906678332</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.539741471773556e-14</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.4880783323372674</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.655594138937705e-15</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.4119449779579998</v>
+      </c>
+      <c r="N40" t="n">
+        <v>9.71003452265194</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.3737223829224459</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.09650607991567513</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8.739152093321668</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.6762776170775542</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.01626927774457558</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.218531379645902e-16</v>
+      </c>
+      <c r="U40" t="n">
+        <v>8.465804905911854e-16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9876372332318251</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.05310537854702167</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.8428883035123231</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9183493595583923</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.106111694413995</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.051435890185346</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-2.090412455971381e-12</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.5031424705901495</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.486471412034243e-13</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.4024450510670541</v>
+      </c>
+      <c r="N41" t="n">
+        <v>9.939244980520073</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.344175697894221</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.08682667019611724</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7.948564109814654</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.7058243021057791</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.01677141568633832</v>
+      </c>
+      <c r="T41" t="n">
+        <v>8.288238040114144e-15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6.968041519904603e-14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.078448021993329</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.05782600118341183</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-1.578078092533172</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9724560383156131</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.164788305926272</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.981576857200884</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.314978551363161e-13</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.173285841411451</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-6.631782043910108e-15</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.4235086431837368</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9.444907493671286</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3758217982105849</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.09977244087327185</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.018423142799116</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.6741782017894151</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.03910952804704838</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.210594014636702e-16</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.771659517121054e-14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.022743387680517</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.006495614470174341</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.987252917527532</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7811156419778201</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.23316680493699</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5.269067267672772</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9.852468853578795e-14</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.9502269531817806</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.306785906894775e-15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.4479100899946697</v>
+      </c>
+      <c r="N43" t="n">
+        <v>8.930363581114065</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.3564096284686057</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.1000706284027139</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6.730932732327228</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6935903715313942</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.03167423177272602</v>
+      </c>
+      <c r="T43" t="n">
+        <v>7.689286356315915e-17</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.284156284526265e-15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.065871225161316</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.02179284011235888</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.627360079458415</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9144331549949757</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.088323026618396</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.791612007341585</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.786828715512681e-11</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.6847450648306711</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-5.173293085415081e-12</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.3957844798831471</v>
+      </c>
+      <c r="N44" t="n">
+        <v>10.1065103874582</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.3714389866559215</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.09215366217320752</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>10.20838799265842</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.6785610133440785</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.0228248354943557</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.724431028471693e-13</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.59560957183756e-12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9996112109834496</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.05411839325242895</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6836172601433095</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7712268644407659</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.161287883168722</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.56000641477804</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-2.755724307670548e-14</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.5838413202336742</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.587845106172098e-14</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.4223512619461483</v>
+      </c>
+      <c r="N45" t="n">
+        <v>9.470789635807348</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.3483484366877997</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.09222613638802875</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>9.439993585221959</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.7016515633122002</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.01946137734112247</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5.292817020573659e-16</v>
+      </c>
+      <c r="U45" t="n">
+        <v>9.185747692235161e-16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.038503626365995</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.01324856588414135</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.179913073333971</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.72280996001343</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.054729184552579</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.511882363621931</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-4.317226660768598e-16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.9599731962906675</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3.856532257026873e-15</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.3831688291363174</v>
+      </c>
+      <c r="N46" t="n">
+        <v>10.43926241261038</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.3619018183157679</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.08692551854432849</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7.488117636378069</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.6880981816842322</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.03199910654302225</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.285510752342291e-16</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.439075553589533e-17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.967805074929862</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.01607531312854341</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.9687252897490248</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9235612188109822</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.234974849753996</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.100043824882844</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.054095166062738e-11</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.7555570346664091</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-3.11423124351799e-13</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.4495343541773921</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8.898096239913851</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.3372645089588027</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.09503856774860138</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>7.899956175117156</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.7127354910411974</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.02518523448888031</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.038077081172663e-14</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.684698388687579e-12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.004565700784753</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.002817694566655704</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.1376227539130062</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.7126638914209187</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.15442312012053</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.361666012721435</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-2.258741021770664e-16</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.12967679668252</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3.853539065654934e-15</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.4193806668735426</v>
+      </c>
+      <c r="N48" t="n">
+        <v>9.53787399003329</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.3500749967485507</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.092031362687549</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>8.638333987278566</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.6999250032514492</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.03765589322275067</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.284513021884978e-16</v>
+      </c>
+      <c r="U48" t="n">
+        <v>7.529136739235547e-18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9432446782038029</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.05918574402222205</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.273149013077894</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9098783389472872</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.039686859400099</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.813295254758528</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8.655431997036371e-17</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.4842067358658385</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.862675103954557e-15</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.3794898114834406</v>
+      </c>
+      <c r="N49" t="n">
+        <v>10.54046730776619</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3287056059707355</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.07819402789280284</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>10.18670474524147</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.7212943940292645</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.01614022452886128</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.287558367984852e-16</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.885143999012124e-18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9201407204036954</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.04224445436517377</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-1.529497588486081</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.7850387394107096</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.064262765225255</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4.543026365520075</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-3.316642360360716e-16</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.7005827295358185</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3.846584847532443e-15</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.3893353945523217</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10.27391808268296</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.3206542480154128</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.07825772863983378</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>7.456973634479925</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.7293457519845873</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.02335275765119395</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.282194949177481e-16</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.105547453453572e-17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.9077208259841938</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.03481361691019125</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.871139320654919</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8462270185253733</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.039787840153384</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.104606993825824</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-7.918423689274233e-15</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.7047899983943178</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.864492790815758e-15</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.3809704600295454</v>
+      </c>
+      <c r="N51" t="n">
+        <v>10.49950159613206</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.3163261147086622</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.07554273474290779</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10.89539300617418</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.7336738852913378</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.02349299994647726</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.288164263605253e-16</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.639474563091411e-16</v>
       </c>
     </row>
   </sheetData>
@@ -3158,31 +6278,31 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4068366650786135</v>
+        <v>0.4063913393569096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01746977914903874</v>
+        <v>0.02661560339910215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4243064442276523</v>
+        <v>0.4539055253964103</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4243064442276523</v>
+        <v>0.4488354901860949</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04485393749314066</v>
+        <v>0.05214749788772585</v>
       </c>
       <c r="H2" t="n">
-        <v>2.658634349602988</v>
+        <v>5.269067267672772</v>
       </c>
       <c r="I2" t="n">
-        <v>9.341365650397012</v>
+        <v>6.730932732327228</v>
       </c>
       <c r="J2" t="n">
-        <v>0.715560596093426</v>
+        <v>0.6689372932783035</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4243064442276523</v>
+        <v>0.4488354901860949</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -3199,7 +6319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3315,55 +6435,55 @@
         <v>0.9523224268498633</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03770708887131363</v>
+        <v>0.02423393716631873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.400402103862616</v>
+        <v>-0.2379819250052098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.756370322009981</v>
+        <v>0.9831732299281261</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06874234197651</v>
+        <v>1.222883288467837</v>
       </c>
       <c r="H2" t="n">
-        <v>2.658634349602988</v>
+        <v>3.304322906408986</v>
       </c>
       <c r="I2" t="n">
-        <v>9.989615409202111e-17</v>
+        <v>4.476784574344764e-12</v>
       </c>
       <c r="J2" t="n">
-        <v>1.34561812479422</v>
+        <v>0.9553718353333818</v>
       </c>
       <c r="K2" t="n">
-        <v>1.036128223452248e-15</v>
+        <v>-2.751677478147776e-14</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3893668859295748</v>
+        <v>0.4455336575479304</v>
       </c>
       <c r="M2" t="n">
-        <v>10.27308714699075</v>
+        <v>8.977997249494749</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3318690554554731</v>
+        <v>0.331869055469902</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08100132831746366</v>
+        <v>0.0926858913473748</v>
       </c>
       <c r="P2" t="n">
-        <v>9.341365650397012</v>
+        <v>8.695677093591014</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.718130944544527</v>
+        <v>0.7181309445300981</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04485393749314066</v>
+        <v>0.03184572784444606</v>
       </c>
       <c r="S2" t="n">
-        <v>3.453760744840826e-17</v>
+        <v>9.172258260492586e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.32987180306737e-18</v>
+        <v>1.492261524781588e-13</v>
       </c>
     </row>
     <row r="3">
@@ -3377,55 +6497,3031 @@
         <v>0.9596982286828247</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04897008694378837</v>
+        <v>-0.005228325494213273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9142421072471785</v>
+        <v>-0.7907865347605347</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7165439881999204</v>
+        <v>0.77339802870779</v>
       </c>
       <c r="G3" t="n">
-        <v>1.164358253718898</v>
+        <v>1.060851969750053</v>
       </c>
       <c r="H3" t="n">
-        <v>2.212684409844941</v>
+        <v>3.893532139456988</v>
       </c>
       <c r="I3" t="n">
-        <v>2.243596228336229e-14</v>
+        <v>1.140347043572175e-16</v>
       </c>
       <c r="J3" t="n">
-        <v>0.695722859086041</v>
+        <v>0.9886287002693678</v>
       </c>
       <c r="K3" t="n">
-        <v>1.13524117002072e-15</v>
+        <v>3.856632831908949e-15</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4243064442276523</v>
+        <v>0.3863368240727492</v>
       </c>
       <c r="M3" t="n">
-        <v>9.427148719562824</v>
+        <v>10.35365956122035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.334439403906574</v>
+        <v>0.3344394038620549</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08895358098469723</v>
+        <v>0.08099345014381293</v>
       </c>
       <c r="P3" t="n">
-        <v>9.78731559015506</v>
+        <v>8.106467860543011</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.715560596093426</v>
+        <v>0.7155605961379452</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0231907619695347</v>
+        <v>0.03295429000897893</v>
       </c>
       <c r="S3" t="n">
-        <v>3.784137233402401e-17</v>
+        <v>1.285544277302983e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>7.478654094454096e-16</v>
+        <v>3.80115681190725e-18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.062845148118856</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04772809765118106</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4533107059615955</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8922345578505793</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.117081095464179</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.910958637724466</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-3.476932991341167e-14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.206986261638216</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.274237816005903e-15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4058485890528634</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.855892233977958</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3703844474440711</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09422868612806551</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9.089041362275534</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6796155525559289</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.04023287538794052</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.424745938668634e-16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.158977663780389e-15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9183831884270194</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04022198456307356</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.8582695778428184</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8080292598298258</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.088762361760061</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.824378932071722</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-3.974778579704026e-13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.273012516216683</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.274147966697914e-14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3981398784071271</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.04672017852401</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3200417763731435</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.07987460167256902</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.175621067928278</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.7299582236268566</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0424337505405561</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.247159888993045e-16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.324926193234675e-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.020020105193131</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01378858386230201</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.63853204033768</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9091970033516752</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.047595221719247</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.639862909378391</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.796872811365531e-14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7669298924632399</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.510214134872906e-14</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.380555630316454</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.51094672257747</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3554606082965004</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.08479612073764514</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10.36013709062161</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6945393917034997</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.02556432974877466</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.034047116243021e-16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9.322909371218436e-16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.045712105362359</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05684145236462675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.847479832792306</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7260748300443259</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.118412867085656</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.46122537693976</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.74660478238093e-17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.564424936631776</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.010912165366173e-15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4061386460479052</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.848853318191001</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.364413857002689</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.09277598052687698</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.53877462306024</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.685586142997311</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.05214749788772585</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.369707217887245e-17</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.248868260793643e-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9375802146733208</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01104744132940376</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.76226053825639</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.840989764061928</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.045407581752856</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.795458565667494</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.286159331159278e-13</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.025684796372473</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.674027821033227e-16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3814450938072939</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.48643701632289</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3267316314825974</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.07812491686003664</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.204541434332506</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.7232683685174026</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.03418949321241578</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.913426070110756e-18</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.287197770530926e-15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9110293254666136</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03190599770583577</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.163761123380084</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8765472411070281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.199751872914643</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.11443557562578</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.20249497041105e-12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.118942002873559</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-3.317667387578575e-15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4391606001702414</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.108285090896258</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3174790731028429</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08739867077453634</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.88556442437422</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7325209268971571</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.03729806676245197</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.105889129192858e-16</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.008316568036835e-14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9549938735812077</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.01113667698244716</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2520927330236313</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8879427207774048</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.153705410406969</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.840871847317237</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.265654081707218e-12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8221104106184941</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.078995578505928e-15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4203400914384868</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.516103822232424</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3328000116037095</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.08769008695062748</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.159128152682763</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7171999883962905</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0274036803539498</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.596651928353092e-17</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.218846939024061e-14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.031486602975119</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.03645961056380737</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.082640917935918</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9078386422514689</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.070782688208963</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.243273274602304</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.17493919648789e-14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6039127504191784</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.756558955355853e-15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3891529965250833</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.27873353522959</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3594564984757814</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.08768656780594906</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.756726725397696</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6905435015242187</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.02013042501397261</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.252186318451951e-16</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.916463988292968e-16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.012453132556086</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.03938675819017985</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.743903074702475</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9674144119003019</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.243276248816004</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.015922882335473</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.293507605490501e-16</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5564875926661516</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.927358624678597e-15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4518957282649883</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.851599394860926</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3528236399492594</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.09994527452896465</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6.984077117664527</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6971763600507407</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.01854958642220505</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.309119541559532e-16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.311692018301669e-18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9300124526610672</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.03825525285228158</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.260789262280481</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7723750629722278</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.086319211117186</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.299366566873276</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.186253435711402e-16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7405250036535284</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.860181016303757e-15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3969114026373693</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10.07781565746276</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3240943878220154</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08063645749628615</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.700633433126724</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7259056121779847</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02468416678845094</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.286727005434586e-16</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.28751145237134e-18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9865261581609575</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.01245666207149262</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1731195132372432</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7459582951999558</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.167814165299733</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.340623692883124</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.89368818515174e-16</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.162392223171917</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.852959968847916e-15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.424497007294537</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9.422916733079829</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3437885060449258</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.09148130238452208</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.659376307116876</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7062114939550742</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.03874640743906391</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.284319989615972e-16</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.63122939505058e-17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.033859459714904</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0464840573866418</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6747630342006934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8171820811638927</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.183305931621063</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.664461627162652</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4.089195645645791e-17</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5901014746344447</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.865357751324869e-15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4301626703433465</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9.298807710539954</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3602834009076397</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.09715011659033988</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9.335538372837348</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6897165990923604</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.01967004915448149</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.288452583774956e-16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.363065215215264e-18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9845569346540256</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.05761071013950942</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.613311707955246</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8706484443067354</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.06630659754416</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.589023443142051</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.892769484571283e-14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4994215765304709</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.536958719134239e-15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3880553265436852</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10.30780839748446</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3431022633506022</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.08346100025610662</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10.41097655685795</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7068977366493978</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.01664738588434903</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.178986239711413e-16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.964256494857094e-15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.026636879854823</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03995963570261046</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.467891854166201</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9881586282761664</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.002940950396953</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.796651136320023</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-6.633415983770086e-13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.043449469318529</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.51082005030593e-15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3641445750762806</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.98464793726109</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3577664479132223</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.08166572209850607</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10.20334886367998</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6922335520867777</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.03478164897728431</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.036066834353099e-17</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.211138661256695e-14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.093487190498735</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.0480706658480831</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.175021661673031</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9131516756849255</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.223153969158284</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.346667758780617</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.09894263004729e-14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4747823213901237</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-7.906938946516838e-14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4460046170168129</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8.968516929348034</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3810627067216965</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1065374150751256</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9.653332241219383</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6689372932783035</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.01582607737967079</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.635646315505613e-15</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.996475433490967e-16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.036612964461925</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.005929855733788542</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.789071426493796</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9215327652008887</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.239104128397907</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.110889061361647</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4.082126377851675e-12</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8042862451176097</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-4.478752507989646e-12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4500840583074406</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8.887228690057103</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3612429530590923</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1019199888898929</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.889110938638353</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.6887570469409077</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.02680954150392032</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.492917502663216e-13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.360708792617225e-13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9783249666160053</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.001380171229923677</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.90654597316875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9918151161431872</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.042557020854498</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.245903489017549</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-2.640606097098242e-16</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7911820103215991</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.929733955849696e-15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3791769686036562</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10.54916381344972</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3409305228874782</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.08103528946008864</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10.75409651098245</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.7090694771125219</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.02637273367738664</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.309911318616565e-16</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8.802020323660806e-18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9374505139440197</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01443268900602748</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4585117966046273</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7803229488275769</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.038401302780963</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.572535697637323</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-9.53896881553969e-15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.130658859170102</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.91234013790437e-15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3788870472172531</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10.55723593790041</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3266864328547442</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.07759026066366187</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9.427464302362678</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.7233135671452557</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.03768862863900339</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.304113379301457e-16</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.179656271846563e-16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9691921331143467</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0004817378881915926</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.6555367391942</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7778384876577633</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.108166854860849</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.781461162747518</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.487322819202191e-15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.025157882589189</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-2.608868889918738e-15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4032630889373812</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9.919082759691623</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.3377478769832202</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.08537829025298875</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.218538837252482</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.7122521230167799</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.03417192941963963</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8.696229633062461e-17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.495774273067397e-16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.002213194713915</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05248117724747617</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.9802848984409387</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8267622512706706</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.149392392037435</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.16842025640733</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.122143926325577e-14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.340269593953248</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.775528298081806e-15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4174995603038805</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9.580848304266175</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.3492551861920419</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.09140400795204888</v>
+      </c>
+      <c r="P23" t="n">
+        <v>7.83157974359267</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.7007448138079582</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.04467565313177493</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.258509432693935e-16</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.740479754418591e-16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.078241881900116</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.03004759132359308</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4830163382651635</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7886260022259199</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.247245656839369</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.938472844849013</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.636085331529849e-15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.216921564917714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.840523109346078e-15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.4535105720910369</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8.820081042747164</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3757499656422727</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1068200343954391</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9.061527155150987</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.6742500343577273</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.04056405216392379</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.280174369782026e-16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.545361777176616e-16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.055112788494538</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.008935979745955891</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.4574395324654419</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8953310155685408</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.240874029338985</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.824153980483951</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.742195631422631e-13</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9268062314453862</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.935551589953936e-15</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.4508156988940261</v>
+      </c>
+      <c r="M25" t="n">
+        <v>8.87280537587324</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.3676898443917073</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1039075294444745</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8.175846019516049</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6823101556082928</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.03089354104817954</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.451838633179787e-17</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.247398543807544e-14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9636293201230749</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.014072656404634</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2135860980378315</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9855141762458608</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.246963209986492</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.316542912575991</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.60666276338432e-11</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8920059418562102</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.106017997846375e-13</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.4539055253964103</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.812406390235674</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3358093260427382</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.09554865454051327</v>
+      </c>
+      <c r="P26" t="n">
+        <v>8.683457087424008</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7141906739572619</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.02973353139520701</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.686726659487916e-15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5.355542544614399e-13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.084843379301365</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0007861789928376231</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.218340262394999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7460534477608073</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.061392353809357</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.242867162866323</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-6.915581612303877e-11</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.025866310308583</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.788975821542714e-13</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3862449921854783</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10.35612121278561</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.3780504773491535</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.09153327583124631</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9.757132837133677</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6719495226508465</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.03419554367695276</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.963252738475714e-15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.305193870767959e-12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9941819770831516</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.05577141706504256</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.296123909659114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8553843046660404</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.149720800447947</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.867755347396106</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.201310388648588e-13</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.317970196606084</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.284450241213097e-15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4177454437329176</v>
+      </c>
+      <c r="M28" t="n">
+        <v>9.575209054857268</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3464564360564671</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.09072494392591375</v>
+      </c>
+      <c r="P28" t="n">
+        <v>10.13224465260389</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.703543563943533</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.04393233988686947</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.094816747071032e-16</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.00436796216196e-15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.038751768440446</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.03280487239690359</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1871479207212308</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9032734296394711</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.108967285928433</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.157924119671752</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-5.989716655907531e-14</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6291165570359142</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.309679691091792e-15</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.4030339334137324</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9.924722522791221</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.3619882919040551</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.09145395466567424</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8.842075880328247</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6880117080959449</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.02097055190119714</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.436559897030597e-16</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.996572218635844e-15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9214414616907176</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0226832564578282</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.169804416217779</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8479532999743397</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.05785057393447</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.813572360418553</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.854336092442527e-14</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.096078923314459</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.081499163363317e-15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.3866906619643057</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10.3441855309298</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.3211075354514141</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.07783600468159958</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10.18642763958145</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.7288924645485859</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.03653596411048198</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.027166387787772e-16</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.951445364147509e-15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9209087116865883</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.006611601467743825</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.3759802836277824</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9741231522682052</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.016344342679179</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.36624110585392</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1.095860396592616e-12</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8594352354586997</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9.733977711065704e-15</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3715700558695607</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10.76512998513119</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.3209218806063773</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.07474917262052197</v>
+      </c>
+      <c r="P31" t="n">
+        <v>8.63375889414608</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.7290781193936227</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.02864784118195666</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.244659237021901e-16</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.652867988642055e-14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9403814895058901</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.05495858531175767</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.897927349273641</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9210693958604375</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.042182093439014</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.178256924396214</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-2.064045708942665e-16</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5076544943074542</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.583487735584002e-15</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3804751198677824</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10.51317101055291</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.3277078347433813</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.07815907936898554</v>
+      </c>
+      <c r="P32" t="n">
+        <v>10.82174307560379</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.7222921652566188</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.01692181647691514</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.194495911861334e-16</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6.880152363142218e-18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.076889934737659</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.02446200002595195</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4206366617041435</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9646530386831706</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.089612932196552</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.033544753789603</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.603818778682494e-16</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6246870710482415</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.730799305354591e-15</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3965248347957794</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10.08764043655849</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.3752788298450969</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.09328048843368966</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8.966455246210398</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.6747211701549032</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.02082290236827472</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.24359976845153e-16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.201272926227498e-17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.035962292296917</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.05126003224819094</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.870791930747273</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.7335294964357321</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.022005432618789</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.41343041733767</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-3.644232809521528e-13</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.500958634038613</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9.627393123722422e-17</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.3710757016944433</v>
+      </c>
+      <c r="M34" t="n">
+        <v>10.77947151390694</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.3610162042692784</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.08397607384655573</v>
+      </c>
+      <c r="P34" t="n">
+        <v>10.58656958266233</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.6889837957307217</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.05003195446795376</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.209131041240807e-18</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.214744269840509e-14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.069847264722887</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03414778289159998</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.824049231774412</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7587290510490128</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.037684747842489</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.217843013407529</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-4.369497988197704e-15</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.302532800968871</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.884544482893964e-15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.3771323153649909</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10.60635695841004</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.3728245725396315</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.08813829172917757</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6.782156986592471</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.6771754274603685</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.0434177600322957</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.294848160964655e-16</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.456499329399235e-16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.028887253841104</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.05846026877635341</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.530770611370802</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.7197112676810835</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.011162871292468</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.801234693063309</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.394618204007597e-16</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5654613176685455</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.854906104027638e-15</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3676836466473951</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.87891722160161</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3585506670816223</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.08264017005832525</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10.19876530693669</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.6914493329183777</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.01884871058895151</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.284968701342546e-16</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4.648727346691988e-18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9813084795351074</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.02440484044047062</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2375087501795061</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9487958495394054</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.155726568423043</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.936461498311879</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.175739702001091e-16</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.67823041887137</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.856296786646905e-15</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.4203930801376322</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9.514904365559062</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.3419702289502701</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.09011772326226393</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9.063538501688122</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.7080297710497299</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.02260768062904567</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.285432262215635e-16</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.05857990066703e-17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.003315638824999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.05882335811441234</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8545561238351889</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9888455985417449</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.123179119966526</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.402613153865445</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.644612368862027e-14</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.4230514717788211</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.845491877831403e-15</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.4084997373249968</v>
+      </c>
+      <c r="M38" t="n">
+        <v>9.791927849617847</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.3496393702503878</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.08953203671343322</v>
+      </c>
+      <c r="P38" t="n">
+        <v>9.597386846134555</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.7003606297496122</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.0141017157259607</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.281830625943801e-16</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.214870789620676e-15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.018688703551181</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.03929603315736935</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.22962009848392</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.7041973063085301</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.060888250774974</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.47195402831268</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-9.963546988317679e-13</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.459143048335486</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.170646571444568e-14</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3852075702469087</v>
+      </c>
+      <c r="M39" t="n">
+        <v>10.38401180037359</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.3549966362111778</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.08572063992020219</v>
+      </c>
+      <c r="P39" t="n">
+        <v>7.52804597168732</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.6950033637888222</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.04863810161118288</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.056882190481523e-15</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.321182329439227e-14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.072423596981526</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.04675588892291244</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1947655039639726</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9367760931614727</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.131587184880575</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.260847906678332</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.539741471773556e-14</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.4880783323372674</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.655594138937705e-15</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.4119449779579998</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9.71003452265194</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.3737223829224459</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.09650607991567513</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8.739152093321668</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.6762776170775542</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.01626927774457558</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.218531379645902e-16</v>
+      </c>
+      <c r="T40" t="n">
+        <v>8.465804905911854e-16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9876372332318251</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.05310537854702167</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.8428883035123231</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9183493595583923</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.106111694413995</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.051435890185346</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-2.090412455971381e-12</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5031424705901495</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.486471412034243e-13</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.4024450510670541</v>
+      </c>
+      <c r="M41" t="n">
+        <v>9.939244980520073</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.344175697894221</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.08682667019611724</v>
+      </c>
+      <c r="P41" t="n">
+        <v>7.948564109814654</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.7058243021057791</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.01677141568633832</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8.288238040114144e-15</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6.968041519904603e-14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.078448021993329</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.05782600118341183</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-1.578078092533172</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9724560383156131</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.164788305926272</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.981576857200884</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.314978551363161e-13</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.173285841411451</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-6.631782043910108e-15</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.4235086431837368</v>
+      </c>
+      <c r="M42" t="n">
+        <v>9.444907493671286</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3758217982105849</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.09977244087327185</v>
+      </c>
+      <c r="P42" t="n">
+        <v>7.018423142799116</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.6741782017894151</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.03910952804704838</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.210594014636702e-16</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.771659517121054e-14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.022743387680517</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.006495614470174341</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.987252917527532</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7811156419778201</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.23316680493699</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5.269067267672772</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.852468853578795e-14</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.9502269531817806</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.306785906894775e-15</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.4479100899946697</v>
+      </c>
+      <c r="M43" t="n">
+        <v>8.930363581114065</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3564096284686057</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.1000706284027139</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6.730932732327228</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.6935903715313942</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.03167423177272602</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7.689286356315915e-17</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.284156284526265e-15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.065871225161316</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.02179284011235888</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.627360079458415</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9144331549949757</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.088323026618396</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.791612007341585</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.786828715512681e-11</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6847450648306711</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-5.173293085415081e-12</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.3957844798831471</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10.1065103874582</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.3714389866559215</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.09215366217320752</v>
+      </c>
+      <c r="P44" t="n">
+        <v>10.20838799265842</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.6785610133440785</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.0228248354943557</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.724431028471693e-13</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.59560957183756e-12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9996112109834496</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.05411839325242895</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6836172601433095</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7712268644407659</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.161287883168722</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.56000641477804</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-2.755724307670548e-14</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5838413202336742</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.587845106172098e-14</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.4223512619461483</v>
+      </c>
+      <c r="M45" t="n">
+        <v>9.470789635807348</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.3483484366877997</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.09222613638802875</v>
+      </c>
+      <c r="P45" t="n">
+        <v>9.439993585221959</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.7016515633122002</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.01946137734112247</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5.292817020573659e-16</v>
+      </c>
+      <c r="T45" t="n">
+        <v>9.185747692235161e-16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.038503626365995</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.01324856588414135</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.179913073333971</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.72280996001343</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.054729184552579</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.511882363621931</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-4.317226660768598e-16</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9599731962906675</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.856532257026873e-15</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.3831688291363174</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10.43926241261038</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.3619018183157679</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.08692551854432849</v>
+      </c>
+      <c r="P46" t="n">
+        <v>7.488117636378069</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.6880981816842322</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.03199910654302225</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.285510752342291e-16</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.439075553589533e-17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.967805074929862</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.01607531312854341</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.9687252897490248</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9235612188109822</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.234974849753996</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.100043824882844</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.054095166062738e-11</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.7555570346664091</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-3.11423124351799e-13</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.4495343541773921</v>
+      </c>
+      <c r="M47" t="n">
+        <v>8.898096239913851</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.3372645089588027</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.09503856774860138</v>
+      </c>
+      <c r="P47" t="n">
+        <v>7.899956175117156</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.7127354910411974</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.02518523448888031</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.038077081172663e-14</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.684698388687579e-12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.004565700784753</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.002817694566655704</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.1376227539130062</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.7126638914209187</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.15442312012053</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.361666012721435</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-2.258741021770664e-16</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.12967679668252</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.853539065654934e-15</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.4193806668735426</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.53787399003329</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.3500749967485507</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.092031362687549</v>
+      </c>
+      <c r="P48" t="n">
+        <v>8.638333987278566</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.6999250032514492</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.03765589322275067</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.284513021884978e-16</v>
+      </c>
+      <c r="T48" t="n">
+        <v>7.529136739235547e-18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9432446782038029</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.05918574402222205</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.273149013077894</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9098783389472872</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.039686859400099</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.813295254758528</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8.655431997036371e-17</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.4842067358658385</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.862675103954557e-15</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.3794898114834406</v>
+      </c>
+      <c r="M49" t="n">
+        <v>10.54046730776619</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.3287056059707355</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.07819402789280284</v>
+      </c>
+      <c r="P49" t="n">
+        <v>10.18670474524147</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.7212943940292645</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.01614022452886128</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.287558367984852e-16</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.885143999012124e-18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9201407204036954</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.04224445436517377</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-1.529497588486081</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.7850387394107096</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.064262765225255</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.543026365520075</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-3.316642360360716e-16</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.7005827295358185</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.846584847532443e-15</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.3893353945523217</v>
+      </c>
+      <c r="M50" t="n">
+        <v>10.27391808268296</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.3206542480154128</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.07825772863983378</v>
+      </c>
+      <c r="P50" t="n">
+        <v>7.456973634479925</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.7293457519845873</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.02335275765119395</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.282194949177481e-16</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.105547453453572e-17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.9077208259841938</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.03481361691019125</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.871139320654919</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8462270185253733</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.039787840153384</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.104606993825824</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-7.918423689274233e-15</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.7047899983943178</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.864492790815758e-15</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.3809704600295454</v>
+      </c>
+      <c r="M51" t="n">
+        <v>10.49950159613206</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.3163261147086622</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.07554273474290779</v>
+      </c>
+      <c r="P51" t="n">
+        <v>10.89539300617418</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.7336738852913378</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.02349299994647726</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.288164263605253e-16</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.639474563091411e-16</v>
       </c>
     </row>
   </sheetData>
@@ -3549,58 +9645,58 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9999999999999925</v>
+        <v>0.07985527476006013</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>-0.2987545356040322</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>-0.005066043622353795</v>
       </c>
       <c r="F2" t="n">
-        <v>-1</v>
+        <v>-0.08975429579616517</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9999999999999989</v>
+        <v>-0.108175273130241</v>
       </c>
       <c r="H2" t="n">
-        <v>-1</v>
+        <v>0.02000202544780255</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.1668519925146892</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.2243209372547108</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>-0.08281065861213792</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>-0.1090478852615445</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.1083076630775609</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9999999999999892</v>
+        <v>0.07985527638785764</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>-0.02939616368815997</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>-0.02000202544780233</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.07985527638785964</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.2243209372547108</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.0966483715756397</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0.1806133504897351</v>
       </c>
     </row>
     <row r="3">
@@ -3610,61 +9706,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999999999999925</v>
+        <v>0.07985527476006013</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.000000000000008</v>
+        <v>0.07800857463402125</v>
       </c>
       <c r="E3" t="n">
-        <v>1.000000000000008</v>
+        <v>0.1192713812555993</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.000000000000008</v>
+        <v>-0.0273739247549008</v>
       </c>
       <c r="G3" t="n">
-        <v>1.000000000000006</v>
+        <v>0.2056172796935209</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.000000000000008</v>
+        <v>0.002132599409989647</v>
       </c>
       <c r="I3" t="n">
-        <v>1.000000000000008</v>
+        <v>-0.1108062283958865</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.000000000000007</v>
+        <v>0.04811997036424798</v>
       </c>
       <c r="K3" t="n">
-        <v>1.000000000000007</v>
+        <v>-0.1947424995164428</v>
       </c>
       <c r="L3" t="n">
-        <v>1.000000000000008</v>
+        <v>0.1808786717789869</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.000000000000009</v>
+        <v>-0.1800347276302527</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9999999999999966</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.000000000000007</v>
+        <v>0.705815532229249</v>
       </c>
       <c r="P3" t="n">
-        <v>1.000000000000008</v>
+        <v>-0.002132599409989415</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.000000000000029</v>
+        <v>-0.9999999999999988</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.000000000000007</v>
+        <v>0.04811997036424808</v>
       </c>
       <c r="S3" t="n">
-        <v>1.000000000000008</v>
+        <v>0.2022511451638528</v>
       </c>
       <c r="T3" t="n">
-        <v>1.000000000000007</v>
+        <v>0.1821190206612581</v>
       </c>
     </row>
     <row r="4">
@@ -3674,61 +9770,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1</v>
+        <v>-0.2987545356040322</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.000000000000008</v>
+        <v>0.07800857463402125</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.1744431764895843</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>-0.1825241707148628</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.999999999999999</v>
+        <v>0.06071002537750956</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.1681714618585764</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>-0.0735284087575258</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.9415016482939613</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>0.05043420843463777</v>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>0.05457256008943789</v>
       </c>
       <c r="M4" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.05035513201054403</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9999999999999893</v>
+        <v>0.07800857197198365</v>
       </c>
       <c r="O4" t="n">
-        <v>-1</v>
+        <v>0.07788119398097158</v>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>-0.1681714618585764</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.07800857197198152</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9415016482939615</v>
       </c>
       <c r="S4" t="n">
-        <v>-1</v>
+        <v>-0.06126935004899387</v>
       </c>
       <c r="T4" t="n">
-        <v>-1</v>
+        <v>-0.01758066328480371</v>
       </c>
     </row>
     <row r="5">
@@ -3738,61 +9834,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>-0.005066043622353795</v>
       </c>
       <c r="C5" t="n">
-        <v>1.000000000000008</v>
+        <v>0.1192713812555993</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
+        <v>-0.1744431764895843</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-1</v>
+        <v>0.1213357922107958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9999999999999989</v>
+        <v>-0.3585162482554572</v>
       </c>
       <c r="H5" t="n">
-        <v>-1</v>
+        <v>-0.9924513100682294</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>-0.05399148088435968</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.1882281910715089</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.01135465123726592</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>-0.3620663882609254</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.3638474451418398</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9999999999999893</v>
+        <v>0.1192713900714326</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.1892841837838078</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9924513100682294</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.1192713900714316</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.1882281910715089</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>-0.01444718375946773</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.09464318332326326</v>
       </c>
     </row>
     <row r="6">
@@ -3802,61 +9898,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1</v>
+        <v>-0.08975429579616517</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.000000000000008</v>
+        <v>-0.0273739247549008</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>-0.1825241707148628</v>
       </c>
       <c r="E6" t="n">
-        <v>-1</v>
+        <v>0.1213357922107958</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9999999999999989</v>
+        <v>0.211255802281903</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>-0.1224750731614977</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>0.1930138000287427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.4859867556015819</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
+        <v>-0.1428248105590818</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
+        <v>0.2157273608797234</v>
       </c>
       <c r="M6" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.2079877864520849</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9999999999999891</v>
+        <v>-0.02737392403210273</v>
       </c>
       <c r="O6" t="n">
-        <v>-1</v>
+        <v>0.1405568992996371</v>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>0.1224750731614977</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.000000000000022</v>
+        <v>0.02737392403210268</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.4859867556015821</v>
       </c>
       <c r="S6" t="n">
-        <v>-1</v>
+        <v>0.1452172620451403</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0.02281118652955155</v>
       </c>
     </row>
     <row r="7">
@@ -3866,61 +9962,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999999999999989</v>
+        <v>-0.108175273130241</v>
       </c>
       <c r="C7" t="n">
-        <v>1.000000000000006</v>
+        <v>0.2056172796935209</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.999999999999999</v>
+        <v>0.06071002537750956</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999999999989</v>
+        <v>-0.3585162482554572</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9999999999999989</v>
+        <v>0.211255802281903</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.386758183777757</v>
       </c>
       <c r="I7" t="n">
-        <v>1.000000000000001</v>
+        <v>0.132128286057212</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.03146863902326603</v>
       </c>
       <c r="K7" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.1292265781685568</v>
       </c>
       <c r="L7" t="n">
-        <v>1.000000000000001</v>
+        <v>0.9993945247415085</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.000000000000002</v>
+        <v>-0.9977140719004173</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9999999999999906</v>
+        <v>0.2056172810122925</v>
       </c>
       <c r="O7" t="n">
-        <v>1.000000000000001</v>
+        <v>0.836944339964894</v>
       </c>
       <c r="P7" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.3867581837777571</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.000000000000023</v>
+        <v>-0.2056172810122931</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.03146863902326606</v>
       </c>
       <c r="S7" t="n">
-        <v>1.000000000000001</v>
+        <v>0.1293572751890301</v>
       </c>
       <c r="T7" t="n">
-        <v>1.000000000000001</v>
+        <v>0.07696329186828042</v>
       </c>
     </row>
     <row r="8">
@@ -3930,61 +10026,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1</v>
+        <v>0.02000202544780255</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.000000000000008</v>
+        <v>0.002132599409989647</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.1681714618585764</v>
       </c>
       <c r="E8" t="n">
-        <v>-1</v>
+        <v>-0.9924513100682294</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>-0.1224750731614977</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.386758183777757</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-1</v>
+        <v>0.04182320354940628</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.1792353697962032</v>
       </c>
       <c r="K8" t="n">
-        <v>-1</v>
+        <v>-0.0366968619334377</v>
       </c>
       <c r="L8" t="n">
-        <v>-1</v>
+        <v>0.3874421637283171</v>
       </c>
       <c r="M8" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.389210022602363</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9999999999999892</v>
+        <v>0.002132590546681777</v>
       </c>
       <c r="O8" t="n">
-        <v>-1</v>
+        <v>0.2775361252155245</v>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.002132590546682902</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0.1792353697962034</v>
       </c>
       <c r="S8" t="n">
-        <v>-1</v>
+        <v>0.0409395740279117</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>-0.07228549743501389</v>
       </c>
     </row>
     <row r="9">
@@ -3994,61 +10090,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.1668519925146892</v>
       </c>
       <c r="C9" t="n">
-        <v>1.000000000000008</v>
+        <v>-0.1108062283958865</v>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>-0.0735284087575258</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>-0.05399148088435968</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>0.1930138000287427</v>
       </c>
       <c r="G9" t="n">
-        <v>1.000000000000001</v>
+        <v>0.132128286057212</v>
       </c>
       <c r="H9" t="n">
-        <v>-1</v>
+        <v>0.04182320354940628</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.1188143648940952</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>-0.3843663668329106</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.1329889489449359</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.132885350675531</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9999999999999892</v>
+        <v>-0.1108062299193297</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.03177598021337441</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.04182320354940631</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.000000000000022</v>
+        <v>0.1108062299193278</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.9999999999999996</v>
+        <v>-0.1188143648940952</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.3421474387155373</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.02555015655644546</v>
       </c>
     </row>
     <row r="10">
@@ -4058,61 +10154,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.2243209372547108</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.000000000000007</v>
+        <v>0.04811997036424798</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9415016482939613</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.1882281910715089</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.4859867556015819</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.03146863902326603</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.1792353697962032</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.1188143648940952</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-1</v>
+        <v>0.102556327757449</v>
       </c>
       <c r="L10" t="n">
-        <v>-1</v>
+        <v>-0.03838785534463942</v>
       </c>
       <c r="M10" t="n">
-        <v>1.000000000000001</v>
+        <v>0.03890593348664572</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9999999999999892</v>
+        <v>0.04811996833416358</v>
       </c>
       <c r="O10" t="n">
-        <v>-1</v>
+        <v>-0.005832858499446492</v>
       </c>
       <c r="P10" t="n">
-        <v>-1</v>
+        <v>-0.1792353697962034</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.04811996833416173</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-1</v>
+        <v>-0.1124998973466267</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>-0.03538539106327082</v>
       </c>
     </row>
     <row r="11">
@@ -4122,61 +10218,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>-0.08281065861213792</v>
       </c>
       <c r="C11" t="n">
-        <v>1.000000000000007</v>
+        <v>-0.1947424995164428</v>
       </c>
       <c r="D11" t="n">
-        <v>-1</v>
+        <v>0.05043420843463777</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.01135465123726592</v>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>-0.1428248105590818</v>
       </c>
       <c r="G11" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.1292265781685568</v>
       </c>
       <c r="H11" t="n">
-        <v>-1</v>
+        <v>-0.0366968619334377</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>-0.3843663668329106</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>0.102556327757449</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>-0.1253580812754889</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.1234728963525577</v>
       </c>
       <c r="N11" t="n">
-        <v>0.999999999999989</v>
+        <v>-0.1947424975462493</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>-0.2032643979638014</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.03669686193343734</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.000000000000021</v>
+        <v>0.1947424975462504</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.9999999999999998</v>
+        <v>0.102556327757449</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>-0.9956670002203095</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>-0.3565812954938257</v>
       </c>
     </row>
     <row r="12">
@@ -4186,61 +10282,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>-0.1090478852615445</v>
       </c>
       <c r="C12" t="n">
-        <v>1.000000000000008</v>
+        <v>0.1808786717789869</v>
       </c>
       <c r="D12" t="n">
-        <v>-1</v>
+        <v>0.05457256008943789</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>-0.3620663882609254</v>
       </c>
       <c r="F12" t="n">
-        <v>-1</v>
+        <v>0.2157273608797234</v>
       </c>
       <c r="G12" t="n">
-        <v>1.000000000000001</v>
+        <v>0.9993945247415085</v>
       </c>
       <c r="H12" t="n">
-        <v>-1</v>
+        <v>0.3874421637283171</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.1329889489449359</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>-0.03838785534463942</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>-0.1253580812754889</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.998338959389405</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9999999999999892</v>
+        <v>0.1808786732460136</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0.8234169804638716</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.3874421637283171</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.1808786732460143</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.03838785534463942</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.1253090031219293</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.07607248463961931</v>
       </c>
     </row>
     <row r="13">
@@ -4250,61 +10346,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.1083076630775609</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.000000000000009</v>
+        <v>-0.1800347276302527</v>
       </c>
       <c r="D13" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.05035513201054403</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.3638474451418398</v>
       </c>
       <c r="F13" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.2079877864520849</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.000000000000002</v>
+        <v>-0.9977140719004173</v>
       </c>
       <c r="H13" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.389210022602363</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.132885350675531</v>
       </c>
       <c r="J13" t="n">
-        <v>1.000000000000001</v>
+        <v>0.03890593348664572</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.000000000000001</v>
+        <v>0.1234728963525577</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.998338959389405</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9999999999999882</v>
+        <v>-0.1800347286166077</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.821547470377577</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.999999999999999</v>
+        <v>0.389210022602363</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.00000000000002</v>
+        <v>0.1800347286166086</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9999999999999989</v>
+        <v>0.03890593348664562</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.1237508511339274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.07295910553143548</v>
       </c>
     </row>
     <row r="14">
@@ -4314,61 +10410,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999999999999892</v>
+        <v>0.07985527638785764</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9999999999999966</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9999999999999893</v>
+        <v>0.07800857197198365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999999999999893</v>
+        <v>0.1192713900714326</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9999999999999891</v>
+        <v>-0.02737392403210273</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9999999999999906</v>
+        <v>0.2056172810122925</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9999999999999892</v>
+        <v>0.002132590546681777</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9999999999999892</v>
+        <v>-0.1108062299193297</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9999999999999892</v>
+        <v>0.04811996833416358</v>
       </c>
       <c r="K14" t="n">
-        <v>0.999999999999989</v>
+        <v>-0.1947424975462493</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9999999999999892</v>
+        <v>0.1808786732460136</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9999999999999882</v>
+        <v>-0.1800347286166077</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.000000000000011</v>
+        <v>0.705815533899707</v>
       </c>
       <c r="P14" t="n">
-        <v>1.000000000000011</v>
+        <v>-0.002132590546681308</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.000000000000032</v>
+        <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.000000000000011</v>
+        <v>0.04811996833416354</v>
       </c>
       <c r="S14" t="n">
-        <v>1.000000000000011</v>
+        <v>0.2022511429791173</v>
       </c>
       <c r="T14" t="n">
-        <v>1.000000000000011</v>
+        <v>0.1821190154855852</v>
       </c>
     </row>
     <row r="15">
@@ -4378,61 +10474,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>-0.02939616368815997</v>
       </c>
       <c r="C15" t="n">
-        <v>1.000000000000007</v>
+        <v>0.705815532229249</v>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>0.07788119398097158</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.1892841837838078</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>0.1405568992996371</v>
       </c>
       <c r="G15" t="n">
-        <v>1.000000000000001</v>
+        <v>0.836944339964894</v>
       </c>
       <c r="H15" t="n">
-        <v>-1</v>
+        <v>0.2775361252155245</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.03177598021337441</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>-0.005832858499446492</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>-0.2032643979638014</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.8234169804638716</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.821547470377577</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000000000000011</v>
+        <v>0.705815533899707</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>-0.2775361252155243</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.7058155338997072</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.005832858499446323</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.2068993052619474</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.1478264609716582</v>
       </c>
     </row>
     <row r="16">
@@ -4442,61 +10538,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>-0.02000202544780233</v>
       </c>
       <c r="C16" t="n">
-        <v>1.000000000000008</v>
+        <v>-0.002132599409989415</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>-0.1681714618585764</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9924513100682294</v>
       </c>
       <c r="F16" t="n">
-        <v>-1</v>
+        <v>0.1224750731614977</v>
       </c>
       <c r="G16" t="n">
-        <v>1.000000000000001</v>
+        <v>-0.3867581837777571</v>
       </c>
       <c r="H16" t="n">
-        <v>-1</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.04182320354940631</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>-0.1792353697962034</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.03669686193343734</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.3874421637283171</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.999999999999999</v>
+        <v>0.389210022602363</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000000000000011</v>
+        <v>-0.002132590546681308</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>-0.2775361252155243</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.000000000000022</v>
+        <v>0.002132590546682692</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.1792353697962034</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.04093957402791143</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.0722854974350139</v>
       </c>
     </row>
     <row r="17">
@@ -4506,61 +10602,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.07985527638785964</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.000000000000029</v>
+        <v>-0.9999999999999988</v>
       </c>
       <c r="D17" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.07800857197198152</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.1192713900714316</v>
       </c>
       <c r="F17" t="n">
-        <v>1.000000000000022</v>
+        <v>0.02737392403210268</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.000000000000023</v>
+        <v>-0.2056172810122931</v>
       </c>
       <c r="H17" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.002132590546682902</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.000000000000022</v>
+        <v>0.1108062299193278</v>
       </c>
       <c r="J17" t="n">
-        <v>1.000000000000022</v>
+        <v>-0.04811996833416173</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.000000000000021</v>
+        <v>0.1947424975462504</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.1808786732460143</v>
       </c>
       <c r="M17" t="n">
-        <v>1.00000000000002</v>
+        <v>0.1800347286166086</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.000000000000032</v>
+        <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.000000000000022</v>
+        <v>-0.7058155338997072</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.000000000000022</v>
+        <v>0.002132590546682692</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9999999999999782</v>
+        <v>-0.04811996833416175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9999999999999784</v>
+        <v>-0.2022511429791183</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9999999999999782</v>
+        <v>-0.1821190154855851</v>
       </c>
     </row>
     <row r="18">
@@ -4570,61 +10666,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.2243209372547108</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.000000000000007</v>
+        <v>0.04811997036424808</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9415016482939615</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.1882281910715089</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.4859867556015821</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.03146863902326606</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0.1792353697962034</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9999999999999996</v>
+        <v>-0.1188143648940952</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9999999999999998</v>
+        <v>0.102556327757449</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.03838785534463942</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9999999999999989</v>
+        <v>0.03890593348664562</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.000000000000011</v>
+        <v>0.04811996833416354</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.005832858499446323</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.1792353697962034</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9999999999999782</v>
+        <v>-0.04811996833416175</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>-1</v>
+        <v>-0.1124998973466267</v>
       </c>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>-0.03538539106327083</v>
       </c>
     </row>
     <row r="19">
@@ -4634,61 +10730,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0.0966483715756397</v>
       </c>
       <c r="C19" t="n">
-        <v>1.000000000000008</v>
+        <v>0.2022511451638528</v>
       </c>
       <c r="D19" t="n">
-        <v>-1</v>
+        <v>-0.06126935004899387</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>-0.01444718375946773</v>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>0.1452172620451403</v>
       </c>
       <c r="G19" t="n">
-        <v>1.000000000000001</v>
+        <v>0.1293572751890301</v>
       </c>
       <c r="H19" t="n">
-        <v>-1</v>
+        <v>0.0409395740279117</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.3421474387155373</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>-0.1124998973466267</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>-0.9956670002203095</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.1253090031219293</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.1237508511339274</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000000000011</v>
+        <v>0.2022511429791173</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.2068993052619474</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9999999999999999</v>
+        <v>-0.04093957402791143</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9999999999999784</v>
+        <v>-0.2022511429791183</v>
       </c>
       <c r="R19" t="n">
-        <v>-1</v>
+        <v>-0.1124998973466267</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.3960350607473532</v>
       </c>
     </row>
     <row r="20">
@@ -4698,58 +10794,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.1806133504897351</v>
       </c>
       <c r="C20" t="n">
-        <v>1.000000000000007</v>
+        <v>0.1821190206612581</v>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>-0.01758066328480371</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.09464318332326326</v>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>0.02281118652955155</v>
       </c>
       <c r="G20" t="n">
-        <v>1.000000000000001</v>
+        <v>0.07696329186828042</v>
       </c>
       <c r="H20" t="n">
-        <v>-1</v>
+        <v>-0.07228549743501389</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.02555015655644546</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>-0.03538539106327082</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>-0.3565812954938257</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.07607248463961931</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9999999999999989</v>
+        <v>-0.07295910553143548</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000000000000011</v>
+        <v>0.1821190154855852</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.1478264609716582</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.0722854974350139</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9999999999999782</v>
+        <v>-0.1821190154855851</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>-0.03538539106327083</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0.3960350607473532</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -4794,7 +10890,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5cb9697-dirty</t>
+          <t>b5c9594-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4827,7 +10923,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3829646626678594</v>
+        <v>0.3829646626598319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4857,7 +10953,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4917,7 +11013,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4932,7 +11028,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4947,7 +11043,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4962,7 +11058,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4977,7 +11073,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08907177338753518</v>
+        <v>0.08907177045543507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4992,7 +11088,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89.07177338753517</v>
+        <v>89.07177045543507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5007,7 +11103,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1963696465783478</v>
+        <v>0.1963696401141736</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5022,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001248044074387546</v>
+        <v>0.001248042840409447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5037,7 +11133,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3645446504338175</v>
+        <v>0.3645446515159374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -5052,7 +11148,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.97259265635919</v>
+        <v>10.97259262371068</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -5067,7 +11163,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.769816175392</v>
+        <v>1.047805349839111</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5082,7 +11178,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -5097,7 +11193,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5112,7 +11208,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5127,7 +11223,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41933.23691995171</v>
+        <v>41933.23557384799</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5142,7 +11238,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5157,7 +11253,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -5172,7 +11268,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5187,7 +11283,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5999999902481539</v>
+        <v>0.5999999902182078</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5202,7 +11298,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.60823526290454</v>
+        <v>64.60823651215563</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5217,7 +11313,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009286741663916792</v>
+        <v>0.009286741483886836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5232,7 +11328,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.389712043725522e-05</v>
+        <v>5.389711694019127e-05</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5278,7 +11374,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.645457929412684</v>
+        <v>1.645457928290766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5293,7 +11389,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1531317527442298</v>
+        <v>0.1531317478285296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5308,7 +11404,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2519718567978555</v>
+        <v>0.2519718485374762</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5323,7 +11419,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.74537383609153</v>
+        <v>10.74537417370354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5338,7 +11434,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8367187539795161</v>
+        <v>0.8367187148415608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5353,7 +11449,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3593336687022275</v>
+        <v>0.3593336654808725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5368,7 +11464,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08983341717555687</v>
+        <v>0.08983341637021813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5383,7 +11479,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03228017136575054</v>
+        <v>0.0322801707869799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5398,7 +11494,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1711121863070972</v>
+        <v>0.1711121874275478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5413,7 +11509,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08555609315354862</v>
+        <v>0.0855560937137739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5428,7 +11524,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01463969015139738</v>
+        <v>0.01463969034312012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5564,28 +11660,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03326028509731693</v>
+        <v>0.03326028400694686</v>
       </c>
       <c r="C2" t="n">
-        <v>33.26028509731692</v>
+        <v>33.26028400694686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0765658763721149</v>
+        <v>0.07656587391426478</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07143269271752828</v>
+        <v>0.0714326926688235</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00727819775170123</v>
+        <v>0.007278197503175589</v>
       </c>
       <c r="H2" t="n">
-        <v>6.705939157817239e-05</v>
+        <v>6.705938507725284e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00734516844918581</v>
+        <v>0.007345168194162157</v>
       </c>
     </row>
     <row r="3">
@@ -5601,7 +11697,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03828293818605745</v>
+        <v>0.03828293695713239</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -5632,7 +11728,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04593952582326894</v>
+        <v>0.04593952434855886</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -5657,13 +11753,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008520468785815645</v>
+        <v>0.008520468433574046</v>
       </c>
       <c r="C5" t="n">
-        <v>8.520468785815645</v>
+        <v>8.520468433574047</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3633593769897581</v>
+        <v>0.3633593574207804</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -5719,28 +11815,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006597909139817421</v>
+        <v>0.00659790892262482</v>
       </c>
       <c r="C7" t="n">
-        <v>6.59790913981742</v>
+        <v>6.59790892262482</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1206126412622277</v>
+        <v>0.1206126357324473</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03031106523982323</v>
+        <v>0.030311065303111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005936539099383243</v>
+        <v>0.0005936538896978842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003385489796629639</v>
+        <v>0.0003385489460493147</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009149015983556316</v>
+        <v>0.0009149015450212645</v>
       </c>
     </row>
     <row r="8">
@@ -5781,13 +11877,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003195736965209304</v>
+        <v>0.00319573690791101</v>
       </c>
       <c r="C9" t="n">
-        <v>3.195736965209304</v>
+        <v>3.195736907911011</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8816354625672945</v>
+        <v>0.8816354230266699</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -5796,13 +11892,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.438870909499721e-05</v>
+        <v>3.438870786188843e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.151541320990989e-06</v>
+        <v>2.151541243881402e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>3.653545681054039e-05</v>
+        <v>3.653545550040796e-05</v>
       </c>
     </row>
     <row r="10">
@@ -5812,28 +11908,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00144932932498834</v>
+        <v>0.001449329343968892</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44932932498834</v>
+        <v>1.449329343968892</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8794968005562904</v>
+        <v>0.8794967616984477</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08555609315354862</v>
+        <v>0.0855560937137739</v>
       </c>
       <c r="G10" t="n">
-        <v>3.537375704520944e-06</v>
+        <v>3.537375797158313e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>4.420360884409003e-06</v>
+        <v>4.42036100018792e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>8.85159173875542e-07</v>
+        <v>8.851591970455608e-07</v>
       </c>
     </row>
     <row r="11">
@@ -5843,13 +11939,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001248044074387546</v>
+        <v>0.001248042840409447</v>
       </c>
       <c r="C11" t="n">
-        <v>1.248044074387546</v>
+        <v>1.248042840409447</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04593952582326894</v>
+        <v>0.04593952434855886</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5880,7 +11976,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4183593769897581</v>
+        <v>0.4183593574207804</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>

--- a/02_Glider_Design/C_results/nausicaa_workflow.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_workflow.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60dcbd7</t>
+          <t>7228918-dirty</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-25T00:47:56.781506+00:00</t>
+          <t>2026-02-25T03:32:37.244642+00:00</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT16"/>
+  <dimension ref="A1:DB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5813,45 +5813,85 @@
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
+          <t>turn_htail_struct_E_pa</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>turn_htail_struct_half_load_n</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>turn_htail_struct_semispan_m</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>turn_htail_struct_thickness_m</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
           <t>turn_htail_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>turn_htail_tip_deflection_proxy_m</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>turn_ixx</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>turn_iyy</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>turn_izz</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>turn_sink_rate_mps</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>turn_w_gust</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_struct_E_pa</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_struct_half_load_n</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_struct_semispan_m</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_struct_thickness_m</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>turn_wing_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>turn_wing_tip_deflection_proxy_m</t>
         </is>
@@ -6009,21 +6049,29 @@
       <c r="CK2" t="inlineStr"/>
       <c r="CL2" t="inlineStr"/>
       <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="n">
-        <v>0.001623521359585303</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.001404676000343176</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.002855703737571289</v>
-      </c>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
       <c r="CQ2" t="inlineStr"/>
       <c r="CR2" t="n">
+        <v>0.001623521359585303</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.001404676000343176</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.002855703737571289</v>
+      </c>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="n">
         <v>-0.1840089401756886</v>
       </c>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6102,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -6126,28 +6174,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>8.000000075441012</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.166562545324026</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.693838288440288</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.002117334595600754</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.090526217921048</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.291454871117319</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.7215029448765478</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.6858003618904708</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.2886948806243109</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.999999924558988</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.1641996381095292</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.2030175405973683</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.1763818290372439</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.02405009816255159</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.01493033863609172</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.0139454964342506</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4.411113740834905e-06</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.03771085639009288</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>103.4305638490439</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.900455139657628</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>45.43371279896174</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>42.56461765567926</v>
+      </c>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
@@ -6174,24 +6266,58 @@
       <c r="CH3" t="inlineStr"/>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
+      <c r="CK3" t="n">
+        <v>3.623275435411836</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>981008.8844269223</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0.1867894784121718</v>
+      </c>
       <c r="CN3" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0.5480756250520061</v>
+      </c>
+      <c r="CR3" t="n">
         <v>0.001805200553987503</v>
       </c>
-      <c r="CO3" t="n">
+      <c r="CS3" t="n">
         <v>0.001807416453427835</v>
       </c>
-      <c r="CP3" t="n">
+      <c r="CT3" t="n">
         <v>0.003389074851215347</v>
       </c>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="n">
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="n">
         <v>0.1086151009467439</v>
       </c>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
+      <c r="CW3" t="n">
+        <v>1286861.725965525</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>0.7471579136486872</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>1.443682025713076</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6417,21 +6543,29 @@
       <c r="CK4" t="inlineStr"/>
       <c r="CL4" t="inlineStr"/>
       <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="n">
-        <v>0.001569168944128617</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0.001456145296075767</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0.003243599982380823</v>
-      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
       <c r="CQ4" t="inlineStr"/>
       <c r="CR4" t="n">
+        <v>0.001569168944128617</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.001456145296075767</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.003243599982380823</v>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="n">
         <v>0.09344722983065679</v>
       </c>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -6501,16 +6635,16 @@
         <v>1.032149310133159</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0.5285991643771197</v>
@@ -6578,28 +6712,72 @@
       <c r="AV5" t="n">
         <v>4.194229221895089</v>
       </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>8.000000068050733</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10.47433050110398</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.574382977904187</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.008443017067042733</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.941770198094932</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.987018664980365</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.8861616802071589</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.6842379648999615</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.3336971259180868</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.999999931949267</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.1657620351000385</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.2662339554993455</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.02953872267357196</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.02182152187729996</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.01161329787063372</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.758961888967236e-05</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.04321149270525246</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>74.9826361640073</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3.240111635621601</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>42.40085508944039</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>37.15566089454248</v>
+      </c>
       <c r="BS5" t="n">
         <v>23.88319845272658</v>
       </c>
@@ -6654,24 +6832,58 @@
       <c r="CJ5" t="n">
         <v>0.8660349776674615</v>
       </c>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
+      <c r="CK5" t="n">
+        <v>3.127500757304741</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>1121259.521889965</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.1863639329118948</v>
+      </c>
       <c r="CN5" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.478428168525546</v>
+      </c>
+      <c r="CR5" t="n">
         <v>0.001915834925895029</v>
       </c>
-      <c r="CO5" t="n">
+      <c r="CS5" t="n">
         <v>0.001750298529663255</v>
       </c>
-      <c r="CP5" t="n">
+      <c r="CT5" t="n">
         <v>0.003301263661187929</v>
       </c>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="n">
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="n">
         <v>0.06498818638547338</v>
       </c>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
+      <c r="CW5" t="n">
+        <v>1375767.212845494</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0.7454557316475792</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.347311249651795</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6897,21 +7109,29 @@
       <c r="CK6" t="inlineStr"/>
       <c r="CL6" t="inlineStr"/>
       <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="n">
-        <v>0.00197425118308107</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0.001578447015359115</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0.003489842664382388</v>
-      </c>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
       <c r="CQ6" t="inlineStr"/>
       <c r="CR6" t="n">
+        <v>0.00197425118308107</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.001578447015359115</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.003489842664382388</v>
+      </c>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="n">
         <v>-0.1601274393629095</v>
       </c>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6981,16 +7201,16 @@
         <v>1.2443079021143</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>6.70174720602557</v>
@@ -7058,28 +7278,72 @@
       <c r="AV7" t="n">
         <v>4.278141190954358</v>
       </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>7.999999225527994</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-4.287147097037822</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.511999614821301</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.002758150460625654</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-4.656376793978115</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.490116186778703</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1.704044128734485</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.6785336111825209</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.2990664282485214</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.000000774472006</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.1714663888174791</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1552125597992705</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.2163372062259568</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.05680147095781617</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.008931556452162129</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.009399999197544378</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5.746146792970111e-06</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.04308136780053428</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>91.32266480179138</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>3.934305310850882</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>37.81564911326416</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>45.17446593437018</v>
+      </c>
       <c r="BS7" t="n">
         <v>29.0375869768198</v>
       </c>
@@ -7134,24 +7398,58 @@
       <c r="CJ7" t="n">
         <v>0.7723824146047078</v>
       </c>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
+      <c r="CK7" t="n">
+        <v>3.460560320132264</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>914539.1546531221</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.1848102536171933</v>
+      </c>
       <c r="CN7" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.5816808658697531</v>
+      </c>
+      <c r="CR7" t="n">
         <v>0.002005686395614048</v>
       </c>
-      <c r="CO7" t="n">
+      <c r="CS7" t="n">
         <v>0.001860355849200065</v>
       </c>
-      <c r="CP7" t="n">
+      <c r="CT7" t="n">
         <v>0.003348760070836334</v>
       </c>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="n">
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="n">
         <v>0.0339039268334492</v>
       </c>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
+      <c r="CW7" t="n">
+        <v>1529720.922407178</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.7392410144687732</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.201613725848522</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7377,21 +7675,29 @@
       <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
       <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="n">
-        <v>0.001801099028849245</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.001680074697064358</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0.003252674252081969</v>
-      </c>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
       <c r="CQ8" t="inlineStr"/>
       <c r="CR8" t="n">
+        <v>0.001801099028849245</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.001680074697064358</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.003252674252081969</v>
+      </c>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="n">
         <v>-0.1108167191287705</v>
       </c>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7461,16 +7767,16 @@
         <v>1.231127229539868</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
         <v>2.71365439699476</v>
@@ -7538,28 +7844,72 @@
       <c r="AV9" t="n">
         <v>4.815661069474015</v>
       </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>8.000000073308197</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.6634402574540854</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.157324872082466</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0.004867962039084794</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.03598467137096306</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.944849419544508</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-1.814657949727906</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.6957538040632926</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.2888476591838561</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.999999926691803</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.1542461959367074</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.001199489045698769</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.2314949806514836</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.06048859832426354</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.001382167203029345</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0190777601501718</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.014158758142665e-05</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.04624519329814437</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>86.04138713971562</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>3.979000579916622</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>36.1372930028249</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>35.77526213988325</v>
+      </c>
       <c r="BS9" t="n">
         <v>22.9958952368049</v>
       </c>
@@ -7614,24 +7964,58 @@
       <c r="CJ9" t="n">
         <v>0.7381020895132383</v>
       </c>
-      <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
+      <c r="CK9" t="n">
+        <v>3.673918005772667</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1051824.381001618</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.1683281654933388</v>
+      </c>
       <c r="CN9" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.4606537128402869</v>
+      </c>
+      <c r="CR9" t="n">
         <v>0.001674582471977474</v>
       </c>
-      <c r="CO9" t="n">
+      <c r="CS9" t="n">
         <v>0.001724237532287904</v>
       </c>
-      <c r="CP9" t="n">
+      <c r="CT9" t="n">
         <v>0.002949236470527871</v>
       </c>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="n">
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="n">
         <v>0.1220703567091277</v>
       </c>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
+      <c r="CW9" t="n">
+        <v>1458004.540782563</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.6733126619733552</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.148283007311202</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7701,16 +8085,16 @@
         <v>1.148181659998692</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
         <v>4.943974160627112</v>
@@ -7778,28 +8162,72 @@
       <c r="AV10" t="n">
         <v>4.688671891418319</v>
       </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>8.000000076352405</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-9.546677196487888</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.624877229870153</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.005101823668855753</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-5.971654835321687</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.82160359135735</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2.909452980364911</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.6215370416359922</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.2510182508444938</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.999999923647595</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2284629583640078</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.1990551611773896</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.2273867863785783</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.09698176601216368</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.01988891082601644</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.01588516089556282</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.062879931011615e-05</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.03845463912979551</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>99.93848652035467</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>3.843098434318172</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>42.59046376786905</v>
+      </c>
       <c r="BS10" t="n">
         <v>27.37662240078971</v>
       </c>
@@ -7854,24 +8282,58 @@
       <c r="CJ10" t="n">
         <v>0.8911002286471551</v>
       </c>
-      <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
+      <c r="CK10" t="n">
+        <v>3.776630009001299</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>888543.3372242888</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.169286262210258</v>
+      </c>
       <c r="CN10" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.548408427855691</v>
+      </c>
+      <c r="CR10" t="n">
         <v>0.001850789160379439</v>
       </c>
-      <c r="CO10" t="n">
+      <c r="CS10" t="n">
         <v>0.001538720678310238</v>
       </c>
-      <c r="CP10" t="n">
+      <c r="CT10" t="n">
         <v>0.003512169223099673</v>
       </c>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="n">
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="n">
         <v>0.05066285114820518</v>
       </c>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
+      <c r="CW10" t="n">
+        <v>1214545.199805354</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.677145048841032</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.38630585782714</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7941,16 +8403,16 @@
         <v>1.034042969920894</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
         <v>3.217129814276742</v>
@@ -8018,28 +8480,72 @@
       <c r="AV11" t="n">
         <v>4.807272432527427</v>
       </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>5.695402414044942</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.035917209125713</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.814753453627861</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.001991886987916373</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0.05737258875965068</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.738439053239764</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.444852072180487</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.5876921018662558</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.1805828869058545</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6.304597585955058</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2623078981337442</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.001912419625321689</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.2579479684413254</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.0814950690726829</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.002158160852345236</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.01211406969505804</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>4.149764558159111e-06</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.02329578300124311</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>163.1264890711018</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>3.800159291155044</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>26.61933448995121</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>36.20738158985117</v>
+      </c>
       <c r="BS11" t="n">
         <v>23.27365626514885</v>
       </c>
@@ -8094,24 +8600,58 @@
       <c r="CJ11" t="n">
         <v>0.5436983452786268</v>
       </c>
-      <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
+      <c r="CK11" t="n">
+        <v>4.963819546773711</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>988272.4359365728</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.1600680056187182</v>
+      </c>
       <c r="CN11" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.466217821028786</v>
+      </c>
+      <c r="CR11" t="n">
         <v>0.001754876651921864</v>
       </c>
-      <c r="CO11" t="n">
+      <c r="CS11" t="n">
         <v>0.001403436701097331</v>
       </c>
-      <c r="CP11" t="n">
+      <c r="CT11" t="n">
         <v>0.00330675745246474</v>
       </c>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="n">
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="n">
         <v>0.1741326025081558</v>
       </c>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
+      <c r="CW11" t="n">
+        <v>1882196.855765816</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.6402720224748729</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.845844470374539</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8181,16 +8721,16 @@
         <v>1.134371252799309</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
         <v>4.6450635553807</v>
@@ -8258,28 +8798,72 @@
       <c r="AV12" t="n">
         <v>4.635075290582289</v>
       </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>8.000000078368897</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-7.095733286002854</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12.32291783426061</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.001032654039843867</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-4.333621449100137</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.951276836586308</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.42510968081595</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.6205374697580379</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.2309246349226377</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.2294625302419621</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.1444540483033379</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.2650425612195436</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.08083698936053167</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.01478277767917261</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.02567274548804293</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.151362583008056e-06</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.02559896351811459</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>153.6030696823638</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3.932079377069244</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>31.33661066887121</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>45.49239727201457</v>
+      </c>
       <c r="BS12" t="n">
         <v>29.24194930138869</v>
       </c>
@@ -8334,24 +8918,58 @@
       <c r="CJ12" t="n">
         <v>0.6400484344842485</v>
       </c>
-      <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
+      <c r="CK12" t="n">
+        <v>4.098646540367313</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>830525.8514484011</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.1690140117557301</v>
+      </c>
       <c r="CN12" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.5857746514174736</v>
+      </c>
+      <c r="CR12" t="n">
         <v>0.001859215924590758</v>
       </c>
-      <c r="CO12" t="n">
+      <c r="CS12" t="n">
         <v>0.001477613785063368</v>
       </c>
-      <c r="CP12" t="n">
+      <c r="CT12" t="n">
         <v>0.003028343139991753</v>
       </c>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="n">
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="n">
         <v>-0.05890039643778217</v>
       </c>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
+      <c r="CW12" t="n">
+        <v>1688217.476214987</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.6760560470229205</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.9957385998718512</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8577,21 +9195,29 @@
       <c r="CK13" t="inlineStr"/>
       <c r="CL13" t="inlineStr"/>
       <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="n">
-        <v>0.001609808845499551</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>0.001588854225845813</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>0.003060960558229133</v>
-      </c>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
+        <v>0.001609808845499551</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.001588854225845813</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.003060960558229133</v>
+      </c>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="n">
         <v>-0.09506102622954878</v>
       </c>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8661,16 +9287,16 @@
         <v>1.221213463311625</v>
       </c>
       <c r="W14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
         <v>6.597709157577377</v>
@@ -8738,28 +9364,72 @@
       <c r="AV14" t="n">
         <v>3.961202393143441</v>
       </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>8.000000077815509</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.88407767610776</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.722146957620863</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.0007609830123539417</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.522242693540188</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.562997918727879</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.4686487977252486</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.6462033166819457</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.2878650926089</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.999999922184491</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.2037966833180542</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.1840747564513396</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.2854332639575959</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.01562162659084162</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.008091828491891166</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.01817113949504346</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.585381275737378e-06</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.03626243843413916</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>97.79278737584454</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>3.546204931519425</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>28.60732696069006</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>45.44472547272004</v>
+      </c>
       <c r="BS14" t="n">
         <v>29.21130645947069</v>
       </c>
@@ -8814,24 +9484,58 @@
       <c r="CJ14" t="n">
         <v>0.5843029748637544</v>
       </c>
-      <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
+      <c r="CK14" t="n">
+        <v>3.423914418790544</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>865784.2199879315</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.176004544840748</v>
+      </c>
       <c r="CN14" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.5851608140888487</v>
+      </c>
+      <c r="CR14" t="n">
         <v>0.001726751195667741</v>
       </c>
-      <c r="CO14" t="n">
+      <c r="CS14" t="n">
         <v>0.00165385429233886</v>
       </c>
-      <c r="CP14" t="n">
+      <c r="CT14" t="n">
         <v>0.003075698314316149</v>
       </c>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="n">
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="n">
         <v>-0.07961199016351639</v>
       </c>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
+      <c r="CW14" t="n">
+        <v>1925769.508176393</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.7040181793629918</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.9090140601009633</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8901,16 +9605,16 @@
         <v>1.01090424458822</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
         <v>2.346724915194509</v>
@@ -8978,28 +9682,72 @@
       <c r="AV15" t="n">
         <v>4.808145342931337</v>
       </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr"/>
-      <c r="BR15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>8.00000005250603</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.982420509312591</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.090052753168568</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.0001978402150110217</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.015713394726708</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.830962920377218</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.8989939425306714</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.5958927188726382</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.1948486946416294</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.99999994749397</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.2541072811273618</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.1671904464908903</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.2276987640125739</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.02996646475102238</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.006213376061067897</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.01060427656910118</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>4.121671146062953e-07</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.02222912389133904</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>172.9407704834397</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>3.844321812940012</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>40.93442766531532</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>32.45386920018659</v>
+      </c>
       <c r="BS15" t="n">
         <v>20.86094500826754</v>
       </c>
@@ -9054,24 +9802,58 @@
       <c r="CJ15" t="n">
         <v>0.8360832835607217</v>
       </c>
-      <c r="CK15" t="inlineStr"/>
-      <c r="CL15" t="inlineStr"/>
-      <c r="CM15" t="inlineStr"/>
+      <c r="CK15" t="n">
+        <v>4.664588106339061</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1117958.196725264</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.1623015913980005</v>
+      </c>
       <c r="CN15" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.4178863954831045</v>
+      </c>
+      <c r="CR15" t="n">
         <v>0.001667586086617603</v>
       </c>
-      <c r="CO15" t="n">
+      <c r="CS15" t="n">
         <v>0.001405713556083972</v>
       </c>
-      <c r="CP15" t="n">
+      <c r="CT15" t="n">
         <v>0.003430797241715257</v>
       </c>
-      <c r="CQ15" t="inlineStr"/>
-      <c r="CR15" t="n">
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="n">
         <v>-0.05612640099800661</v>
       </c>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
+      <c r="CW15" t="n">
+        <v>1241057.086708934</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.6492063655920018</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.300714685475105</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9141,16 +9923,16 @@
         <v>1.185119383900497</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
       </c>
       <c r="Z16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>4.923732910308015</v>
@@ -9218,28 +10000,72 @@
       <c r="AV16" t="n">
         <v>4.266409264797456</v>
       </c>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
-      <c r="BR16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>5.786276338250591</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.6135681858797716</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12.56998640456643</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.006083729662574829</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.02284257758698438</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9.682878857592529</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-2.877374678413959</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.6231692216568206</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.240361331063158</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.213723661749409</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.2268307783431793</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.0007614192528994794</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.3227626285864176</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.09591248928046531</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.001278267053916191</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02618747167618007</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.267443679703089e-05</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.0184233534759406</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>201.7190632576912</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3.716341605232067</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>40.84194333314971</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>38.33364253090253</v>
+      </c>
       <c r="BS16" t="n">
         <v>24.6403904530171</v>
       </c>
@@ -9294,24 +10120,58 @@
       <c r="CJ16" t="n">
         <v>0.8341942965020249</v>
       </c>
-      <c r="CK16" t="inlineStr"/>
-      <c r="CL16" t="inlineStr"/>
-      <c r="CM16" t="inlineStr"/>
+      <c r="CK16" t="n">
+        <v>3.954432050276107</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>989805.4831460315</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.1697308070232252</v>
+      </c>
       <c r="CN16" t="n">
+        <v>0.1609539963114405</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.01287631970491524</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.4935962366818373</v>
+      </c>
+      <c r="CR16" t="n">
         <v>0.001733613400268426</v>
       </c>
-      <c r="CO16" t="n">
+      <c r="CS16" t="n">
         <v>0.001618580530186619</v>
       </c>
-      <c r="CP16" t="n">
+      <c r="CT16" t="n">
         <v>0.003287628204115784</v>
       </c>
-      <c r="CQ16" t="inlineStr"/>
-      <c r="CR16" t="n">
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="n">
         <v>0.1206618374050868</v>
       </c>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
+      <c r="CW16" t="n">
+        <v>1300804.351221048</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0.678923228092901</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.397194598673121</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0.03177556789384968</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1.29777594329926</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9414,22 +10274,46 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6927854609944722</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09941531273895929</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8508253050163355</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.826019105469479</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04624519329814437</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2674568730061401</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.70174720602557</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.29825279397443</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5482591182115156</v>
+      </c>
       <c r="O2" t="n">
-        <v>1001000</v>
+        <v>400.8260191054695</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -9685,47 +10569,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.8508253050163355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.02782467804476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05318502778566447</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.346730071231464</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9853477478517625</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9893309756438055</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9448898382170666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.6950755029061</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.0660922405638189</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.4679297526098196</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9767912330499453</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9873493148145965</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9082551991459638</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.283846338784262</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8657842199879315</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.2381724304419578</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.07961199016351639</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.221213463311625</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.597709157577377</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.402290842422623</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.4738506753585526</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5761493246414474</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8508253050163355</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.034609600642095e-16</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.2200799677989251</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.62193288008469e-17</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02277931917802112</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8.000000077815509</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.999999922184491</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.6462033166819457</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2037966833180542</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1840747564513396</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2854332639575959</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.01562162659084162</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>28.60732696069006</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>45.44472547272004</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.03626243843413916</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9741,47 +10707,129 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>5.29825279397443</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.079247922804122</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.005335858104649052</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5812327858320741</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9801366995621699</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8733501948164859</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.889367305813166</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.4543865877499265</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.54956044416261</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1.701591119890291</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.08052006441104</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.057711991054487</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.941772511458981</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.019813948271452</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9145391546531221</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.1460879400577341</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.0339039268334492</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.2443079021143</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.70174720602557</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.29825279397443</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4975579672990667</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5524420327009334</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.7977852421852994</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.850371707708594e-18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0391447169740097</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.404683942183814e-16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.02448668538292283</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.999999225527994</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4.000000774472006</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.6785336111825209</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1714663888174791</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.1552125597992705</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.2163372062259568</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.05680147095781617</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>37.81564911326416</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>45.17446593437018</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.04308136780053428</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9797,47 +10845,129 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0.5482591182115156</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.088321040332457</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0598632735939427</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.965250368583927</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9388904135432066</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9260326729701467</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8941695594118204</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1075217023251955</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.824957895792465</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.8786121913562148</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.023509998008188</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9868422341051831</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9206750728332104</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.917178141896996</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.121259521889965</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2384489446171719</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.06498818638547338</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.032149310133159</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5285991643771197</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>11.47140083562288</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5017408817884844</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5482591182115156</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8012129059226224</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>8.095376221225099e-17</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2674568730061401</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.036208156316813e-16</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.02395588353664308</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.000000068050733</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.999999931949267</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.6842379648999615</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1657620351000385</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2662339554993455</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.02953872267357196</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>42.40085508944039</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>37.15566089454248</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.04321149270525246</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9853,47 +10983,129 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9870016275719961</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01606662293730111</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3102689514734824</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8875259509371421</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8682206020721495</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9740388198738045</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.964025983155878</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-2.747734304761066</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.424103835693643</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.095224096300989</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9186195642190002</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.9312588506799628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.125478317476658</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8305258514484011</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.007151774483256101</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.05890039643778217</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.134371252799309</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.6450635553807</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.3549364446193</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.4550303155633375</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5949696844366625</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6436892886044281</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7.401486830834377e-18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.04886041372366297</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.072416312633626e-16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.02324645296907375</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>8.000000078368897</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.6205374697580379</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2294625302419621</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.1444540483033379</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.2650425612195436</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.08083698936053167</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>31.33661066887121</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>45.49239727201457</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.02559896351811459</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9909,47 +11121,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.088321040332457</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0598632735939427</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.965250368583927</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9388904135432066</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9260326729701467</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8941695594118204</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1075217023251955</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.824957895792465</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.8786121913562148</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.023509998008188</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9868422341051831</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.9206750728332104</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.917178141896996</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.121259521889965</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2384489446171719</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.06498818638547338</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.032149310133159</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5285991643771197</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>11.47140083562288</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5017408817884844</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5482591182115156</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8012129059226224</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8.095376221225099e-17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.2674568730061401</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.036208156316813e-16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02395588353664308</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.000000068050733</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.999999931949267</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.6842379648999615</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1657620351000385</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.2662339554993455</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.02953872267357196</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>42.40085508944039</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>37.15566089454248</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.04321149270525246</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9965,47 +11259,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>0.3227626285864176</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9911875414397531</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04369259555608837</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.4496683858031161</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9218529612038607</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8979554619093665</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8947832301496469</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5884622266407327</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.60440909051438</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-2.882818297692795</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.016921546365891</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.002007800848873</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.006723164523646</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8672029008140318</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9898054831460315</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0281372880259263</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1206618374050868</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.185119383900497</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.923732910308015</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.076267089691985</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.4569601175769782</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5930398824230219</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6812552593138042</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.06832413744322403</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.144832625267251e-16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.02182616756893173</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.786276338250591</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>6.213723661749409</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.6231692216568206</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2268307783431793</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0007614192528994794</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.3227626285864176</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.09591248928046531</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>40.84194333314971</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>38.33364253090253</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.0184233534759406</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,47 +11397,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0.09698176601216368</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9885915054698982</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.008121771439608752</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.4860041684178347</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9098214223220454</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9947994817501918</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.997503624238794</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.714116590036362</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.7636203253263165</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-2.904363892765</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.08850668696362</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9550707420757844</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.078305343340344</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8096967998702361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8885433372242888</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03628178046860997</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.05066285114820518</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.148181659998692</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.943974160627112</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.056025839372888</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.4557632858063316</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5942367141936684</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6519153050889409</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.480297366166875e-17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.04462459433433549</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.02321793152099786</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.000000076352405</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3.999999923647595</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.6215370416359922</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2284629583640078</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.1990551611773896</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.2273867863785783</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.09698176601216368</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>42.59046376786905</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.03845463912979551</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10077,47 +11535,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9885915054698982</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008121771439608752</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4860041684178347</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9098214223220454</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9947994817501918</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.997503624238794</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.714116590036362</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.7636203253263165</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2.904363892765</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.08850668696362</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9550707420757844</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.078305343340344</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8096967998702361</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8885433372242888</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.03628178046860997</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.05066285114820518</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.148181659998692</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.943974160627112</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.056025839372888</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.4557632858063316</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5942367141936684</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6519153050889409</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.480297366166875e-17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.04462459433433549</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.02321793152099786</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.000000076352405</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3.999999923647595</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.6215370416359922</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2284629583640078</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1990551611773896</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.2273867863785783</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.09698176601216368</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>42.59046376786905</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.03845463912979551</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10133,47 +11673,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>45.49239727201457</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9870016275719961</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01606662293730111</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3102689514734824</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8875259509371421</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8682206020721495</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9740388198738045</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.964025983155878</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-2.747734304761066</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.424103835693643</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.095224096300989</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9186195642190002</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9312588506799628</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.125478317476658</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8305258514484011</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.007151774483256101</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.05890039643778217</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.134371252799309</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.6450635553807</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.3549364446193</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4550303155633375</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5949696844366625</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6436892886044281</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7.401486830834377e-18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04886041372366297</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.072416312633626e-16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.02324645296907375</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8.000000078368897</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.6205374697580379</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2294625302419621</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1444540483033379</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.2650425612195436</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.08083698936053167</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>31.33661066887121</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>45.49239727201457</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.02559896351811459</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10189,47 +11811,129 @@
           <t>max</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>0.04624519329814437</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9829964485326228</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.02026891872408031</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.139494996289268</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8664370557564435</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8641496501236114</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8727132257369257</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.6108138947097776</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.9684496647338001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.810409614874011</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.990479795321914</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.076310980174726</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.9106276770559846</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.9720030271883751</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.051824381001619</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2770175420652068</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1220703567091277</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.231127229539868</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.71365439699476</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.286345603005241</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4531838364355464</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5968161635644536</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6946604639966178</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7.401486830834377e-18</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.03097740880859888</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.700743415417189e-16</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.0210375388516662</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>8.000000073308197</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>3.999999926691803</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.6957538040632926</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1542461959367074</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.001199489045698769</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.2314949806514836</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.06048859832426354</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>36.1372930028249</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>35.77526213988325</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.04624519329814437</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10242,7 +11946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10440,6 +12144,1077 @@
         <is>
           <t>turn_htail_deflection_proxy_over_allow</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.088321040332457</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0598632735939427</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.965250368583927</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9388904135432066</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9260326729701467</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8941695594118204</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1075217023251955</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.824957895792465</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.8786121913562148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.917178141896996</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.121259521889965</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2384489446171719</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06498818638547338</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.032149310133159</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5285991643771197</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.42861286636753e-15</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8.023706190184203</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-3.108624468950438e-15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.8012129059226224</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.866106145117253</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5017408817884844</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.1633689166276266</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.47140083562288</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5482591182115156</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.000000068050733</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.941770198094932</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.987018664980365</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.8861616802071589</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.6842379648999615</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3336971259180868</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.999999931949267</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1657620351000385</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3313923399364977</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2662339554993455</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.02953872267357196</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>42.40085508944039</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>37.15566089454248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.079247922804122</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.005335858104649052</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5812327858320741</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9801366995621699</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8733501948164859</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.889367305813166</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.4543865877499265</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.54956044416261</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.701591119890291</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.019813948271452</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9145391546531221</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1460879400577341</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0339039268334492</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.2443079021143</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.70174720602557</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.174341509220291</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.021405182655144e-14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.7977852421852994</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.89130972055222</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.4975579672990667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.1613138613922337</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.29825279397443</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5524420327009334</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.999999225527994</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-4.656376793978115</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.490116186778703</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.704044128734485</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.6785336111825209</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.2990664282485214</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.000000774472006</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1714663888174791</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1552125597992705</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2163372062259568</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05680147095781617</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>37.81564911326416</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>45.17446593437018</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9829964485326228</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02026891872408031</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.139494996289268</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8664370557564435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8641496501236114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8727132257369257</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.6108138947097776</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.9684496647338001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1.810409614874011</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9720030271883751</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.051824381001619</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2770175420652068</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1220703567091277</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.231127229539868</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.71365439699476</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9293222642579664</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.110223024625157e-14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6946604639966178</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.765895267300853</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.4531838364355464</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1279348894613601</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.286345603005241</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5968161635644536</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.000000073308197</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.03598467137096306</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.944849419544508</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.814657949727906</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6957538040632926</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2888476591838561</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.999999926691803</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1542461959367074</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.001199489045698769</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2314949806514836</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.06048859832426354</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36.1372930028249</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>35.77526213988325</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9885915054698982</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.008121771439608752</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.4860041684178347</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9098214223220454</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9947994817501918</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.997503624238794</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.714116590036362</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.7636203253263165</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-2.904363892765</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8096967998702361</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8885433372242888</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03628178046860997</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05066285114820518</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.148181659998692</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.943974160627112</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.338737830030065</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-6.661338147750939e-15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.6519153050889409</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.209525395666883</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4557632858063316</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1207459350344579</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.056025839372888</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5942367141936684</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.000000076352405</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-5.971654835321687</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.82160359135735</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2.909452980364911</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.6215370416359922</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.2510182508444938</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.999999923647595</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2284629583640078</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1990551611773896</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2273867863785783</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.09698176601216368</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>43.62804348480163</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>42.59046376786905</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9347590795975648</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01616049041578577</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.315826814186654</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9387404040914954</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9151598704211585</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8762864426443511</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.029829928259657</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.417010036086706</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.446597535743278</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.254797903843877</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9882724359365729</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2254378914854979</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1741326025081558</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.034042969920894</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.217129814276742</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.661338147750939e-16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.042333718128063</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.4210854715202e-14</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5604206281880757</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.386557717571922</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.430945306413369</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.09814728089125868</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.782870185723258</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.619054693586631</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.695402414044942</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.05737258875965068</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.738439053239764</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.444852072180487</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5876921018662558</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1805828869058545</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.304597585955058</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.2623078981337442</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.001912419625321689</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2579479684413254</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0814950690726829</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>26.61933448995121</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>36.20738158985117</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9870016275719961</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01606662293730111</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3102689514734824</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8875259509371421</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8682206020721495</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9740388198738045</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.964025983155878</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.747734304761066</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.424103835693643</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.125478317476658</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8305258514484011</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.007151774483256101</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.05890039643778217</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.134371252799309</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.6450635553807</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.465812411709889</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-6.217248937900877e-15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6436892886044281</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.301659401788937</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4550303155633375</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.119030598819186</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.3549364446193</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.5949696844366625</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.000000078368897</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-4.333621449100137</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.951276836586308</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.42510968081595</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.6205374697580379</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2309246349226377</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.999999921631103</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.2294625302419621</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1444540483033379</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2650425612195436</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.08083698936053167</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>31.33661066887121</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>45.49239727201457</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.02782467804476</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05318502778566447</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.346730071231464</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9853477478517625</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9893309756438055</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9448898382170666</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.6950755029061</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.0660922405638189</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.4679297526098196</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.283846338784262</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8657842199879315</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.2381724304419578</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.07961199016351639</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.221213463311625</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.597709157577377</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-9.103828801926284e-15</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6.602399033967753</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-2.886579864025407e-15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.8508253050163355</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.524048145223407</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.4738506753585526</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1638414965956791</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.402290842422623</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.5761493246414474</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.000000077815509</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.522242693540188</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.562997918727879</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.4686487977252486</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.6462033166819457</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2878650926089</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.999999922184491</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.2037966833180542</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1840747564513396</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2854332639575959</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01562162659084162</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>28.60732696069006</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>45.44472547272004</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9478026892756747</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.01092685451201855</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2236509674815741</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9086544445702548</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8852291589591004</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9513839201480557</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.305723743362339</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.325099802632354</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8988057205313513</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8273713911392895</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.117958196725264</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1755437022704112</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.05612640099800661</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.01090424458822</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.346724915194509</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.098127167667972</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-6.994405055138486e-15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5533047506341265</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8.494414584998756</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.4369587086181987</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.09825322245833133</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.653275084805491</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.6130412913818013</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.00000005250603</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.015713394726708</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.830962920377218</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8989939425306714</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5958927188726382</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1948486946416294</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.99999994749397</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.2541072811273618</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1671904464908903</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2276987640125739</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02996646475102238</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>40.93442766531532</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>32.45386920018659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9911875414397531</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04369259555608837</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.4496683858031161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9218529612038607</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8979554619093665</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8947832301496469</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5884622266407327</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.60440909051438</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.882818297692795</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8672029008140318</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9898054831460315</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0281372880259263</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1206618374050868</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.185119383900497</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.923732910308015</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.049724123296721</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.243449787580175e-14</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.6812552593138042</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.899029228653329</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.4569601175769782</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.126511548070186</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.076267089691985</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.5930398824230219</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.786276338250591</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.02284257758698438</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.682878857592529</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-2.877374678413959</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6231692216568206</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.240361331063158</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.213723661749409</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.2268307783431793</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.0007614192528994794</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.3227626285864176</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.09591248928046531</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40.84194333314971</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>38.33364253090253</v>
       </c>
     </row>
   </sheetData>
@@ -10453,9 +13228,4800 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mass_scale</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cg_x_shift_mac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>incidence_bias_deg</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>eff_a</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>eff_e</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>eff_r</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bias_a_deg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bias_e_deg</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>bias_r_deg</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>wing_E_scale</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>htail_E_scale</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>w_gust_nom</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>w_gust_turn</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>drag_factor</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_deg</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_a_deg</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_e_deg</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_r_deg</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>nom_sink_rate_mps</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>nom_L_over_D</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>nom_CL</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>nom_D</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_margin_deg</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>nom_cl_margin_to_cap</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>turn_alpha_deg</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_a_deg</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_e_deg</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_r_deg</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>turn_CL</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>turn_D</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>turn_alpha_margin_deg</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>turn_cl_margin_to_cap</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_a</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_e</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_r</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_deflection_proxy_over_allow</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>turn_htail_deflection_proxy_over_allow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.6323336300154776</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04949884127041029</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.2607072578013038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.09435063956970134</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06466740162857487</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3129636981188195</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4614606279332585</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.4209890445125096</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1454315042485784</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0548878036156314</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.167827345854965</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.2497605474849804</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.2783353936130029</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.004943669007177508</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3020922449780772</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.4014455975222316</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.254011483537437</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.549120350089117</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.3949052624839888</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4119425645324213</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.6323336311502682</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.4759206927267052</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.3020922449780769</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6323336311502695</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.3779015287250502</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.01641054682634579</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4915904771389252</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.1469740947035262</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.6724399739728355</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.6424114596003598</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.3779015287250502</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.6724399739728358</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.4382743889083938</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4915904771389256</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.117496327546919</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.1984590605862184</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.1001398054301394</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>mass_scale</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.6323336300154776</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5526790607100831</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7644435104867838</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5327457394025735</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.09824346911510462</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.1752077086170759</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.1800994862982394</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2612410267471446</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.4117798318371904</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.04669495819585822</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.03946968102593949</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.3704587099451963</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.1650657965308676</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3278008435688612</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1272848259658045</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.08745563285236241</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6298130794149288</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5127027321388722</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.882012216217645</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.883717634490259</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9380036671794407</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.1272848259658047</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.9999999999999997</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.4355362400081345</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2271364705916465</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.001501066533709819</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.4124394131182822</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.7556876367965371</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9010614530522529</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.4355362400081345</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.7556876367965372</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6333934400563377</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.001501066533710352</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.3935886789888393</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2921053514105905</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.452478823289782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>cg_x_shift_mac</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.04949884127041029</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5526790607100831</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7225046497736651</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3958805234554383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4601086994956413</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1270394729442995</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2277583676498626</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1338160408247711</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.2399914439362714</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04406544833548062</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.08855921460962191</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.3562471391747686</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.257864282196233</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03501741600656758</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04427991885299578</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.3619597769478439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8457736677527872</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.2587778782229514</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6267494588433714</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.6212620326209123</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5526790592065031</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.6185130375315685</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.04427991885299579</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.5526790592065015</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01989204298696813</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5052754790452935</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.7171658090957048</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.2398086160001855</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1925054062235446</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.4949718415819724</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.01989204298696813</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.1925054062235445</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5062053789809247</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.7171658090957043</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.2802059847529678</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1373403271209359</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3104835129623918</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>incidence_bias_deg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.2607072578013038</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7644435104867838</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7225046497736651</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5283876042127947</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2438439341727359</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1798100471679534</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2456401931589031</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2809423825626706</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.01557895016114425</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.04601345655305488</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02507497133146509</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.3906103692829024</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.6097093867996546</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.07384300833206615</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.02095703153331036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.2777763140759901</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8214293357776151</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1414807618626842</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.693283656233855</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6453922249448217</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7644435093594708</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.7368704817016303</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.02095703153331021</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.7644435093594701</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5233083812020192</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5684103682387143</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1440169393177145</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.01601863662038023</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3641142814686275</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.6145499840364886</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.5233083812020192</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.3641142814686273</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.8547901357398259</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.144016939317714</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.7016566579253276</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1676496820101165</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3318118594167773</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>eff_a</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.09435063956970134</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5327457394025735</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3958805234554383</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5283876042127947</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4123140508418879</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.1405339804212794</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.1459867945500135</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5146049533568284</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.06211700135871172</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4209469587776781</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.2326895814758219</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.6434219521500937</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1871962062795376</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1537295004398183</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4783508849486027</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.5163676029087079</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.474024985832473</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.01110018623663566</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5928765450455016</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.5117238453719</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5327457403651186</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.6052393838982794</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.4783508849486028</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.532745740365118</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.05888169437746115</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.2260909506616824</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1440238720479926</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.0621306215879416</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.07478846560194653</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.2822156962284013</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.05888169437746115</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.07478846560194674</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.324268616015381</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.1440238720479921</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.417500246311398</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.2220347781533375</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4234702396020608</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>eff_e</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.06466740162857487</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09824346911510462</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4601086994956413</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2438439341727359</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4123140508418879</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4624133896527334</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4342392186854072</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.005472300414354474</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.2634992887018894</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1043818559813038</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.29517789493472</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.3399684714431901</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1541101352642322</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.005518282565850646</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2321964767408604</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.5117704474277378</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.47599895171627</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.3232238354603366</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.283136973365745</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2510940835239076</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0982434699135355</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2390584507190955</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.2321964767408603</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.09824346991353594</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.06817258998359825</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1442857179695738</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1618611448733983</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.2639326718185028</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.1595207514416855</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1311229802519437</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.06817258998359825</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1595207514416852</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3986392115562608</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1618611448733981</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.10370030232325</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.01792155693698842</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.2934574525642376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>eff_r</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3129636981188195</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.1752077086170759</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1270394729442995</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1798100471679534</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.1405339804212794</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4624133896527334</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9548874462927077</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.4040515761734069</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.07505573994978584</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.1743923685421103</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.4879073511166243</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.369375711599631</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.6853934730624766</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.08574665622217023</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2648599069758623</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.2040537154341386</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.04295484120126973</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.2810482472316055</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.1623472317239822</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1540553686609466</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.1752077084033823</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.1791086307265989</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.2648599069758623</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1752077084033816</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.4481298887563213</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.2662839043227594</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.1226408583248415</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.07514810458635132</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.4132967534265909</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.2192296709863068</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.4481298887563213</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.4132967534265911</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.4277450841542153</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.1226408583248411</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.08509743124589217</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1580938818146259</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.3992166788083074</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bias_a_deg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4614606279332585</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.1800994862982394</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2277583676498626</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2456401931589031</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1459867945500135</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4342392186854072</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9548874462927077</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.3879997693832046</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.0143676069423651</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.2986139169631065</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.3156717518430144</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.3426151452041679</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.7294817736314603</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.110278360469406</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1961818237894118</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.2416274990040327</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.03129633832426991</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.3095685179641162</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.1435978099186787</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1419244534571302</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.18009948675122</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.1664532322572654</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.1961818237894117</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.18009948675122</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4255507246605898</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.08283774629124388</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.00244471304875248</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.01403553289964021</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.4059389105538061</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2051086158353365</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.4255507246605898</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4059389105538065</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4215511243353974</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.002444713048752145</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.0369371518225427</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2754061300662249</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.2485042607621609</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bias_e_deg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4209890445125096</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2612410267471446</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1338160408247711</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2809423825626706</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5146049533568284</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005472300414354474</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.4040515761734069</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3879997693832046</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.152366150604913</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.006292978353160682</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5512966050657544</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2276486675160709</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1397306817943849</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4798399653174872</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.3438211252280233</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2130655323741962</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2330190229921311</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.08006325483782156</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.05736411859110101</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.03266764245948673</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.261241027732491</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1400056957961414</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3438211252280232</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.2612410277324909</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.001621764008553666</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4604233646733658</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.3820983595812321</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.151521110768691</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.05633434435437317</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.07909825055794842</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.001621764008553666</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.05633434435437332</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.338497707195412</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.3820983595812325</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.5002206080030146</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.08701071515137776</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.3811136755856935</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bias_r_deg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1454315042485784</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.4117798318371904</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2399914439362714</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.01557895016114425</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.06211700135871172</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2634992887018894</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.07505573994978584</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.0143676069423651</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.152366150604913</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5833317733807006</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.05542004062879684</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1605048665302865</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.241307113623562</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5544230703940533</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.2186475821255895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01904522046582025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.08270056165868929</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.3515098139712672</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.44176953644817</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5028356175743663</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.4117798323008935</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.4311890865821416</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.2186475821255896</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4117798323008938</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1038248129807936</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1225213764440871</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.03738081822922935</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9999983251136108</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5027708858715679</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5479155075413978</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.1038248129807936</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.5027708858715675</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.04155317726218683</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.03738081822922917</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1573063403644544</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.6708344977861006</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.09159666937122866</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>wing_E_scale</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0548878036156314</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.04669495819585822</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04406544833548062</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.04601345655305488</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4209469587776781</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1043818559813038</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.1743923685421103</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.2986139169631065</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.006292978353160682</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5833317733807006</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.468194459336847</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.3436444780786522</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1006543162427618</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1433577675608064</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3363563335652405</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.5919100597908437</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1921715976841662</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.05385418484894396</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2096691688293588</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1513530209804821</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.04669495819636894</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1521424321389192</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.3363563335652404</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.04669495819636869</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1797033954963047</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.04161326125097158</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.2174293059873264</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.5833690735283977</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.09081843054350537</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.08753317148258534</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.1797033954963047</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.09081843054350495</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.19237994105271</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.2174293059873263</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.2030496439843069</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.963451109993147</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.3964912550450069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>htail_E_scale</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.167827345854965</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.03946968102593949</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.08855921460962191</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02507497133146509</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.2326895814758219</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.29517789493472</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4879073511166243</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.3156717518430144</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5512966050657544</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.05542004062879684</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.468194459336847</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.7662734775557207</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3352871446537484</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.5465534652308619</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.8355294643232462</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4998057662845655</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1485648886518352</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.02305514865496865</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.2082812032563501</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2337601809647161</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.03946968214000521</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1554086424274072</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.8355294643232462</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.03946968214000619</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.07790797825568674</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6542103990553929</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.104863491325826</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.05587948899151336</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1458277293380356</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.04358614016321346</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.07790797825568674</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.1458277293380352</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.0602603957490512</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.1048634913258264</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.348003792600847</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.4314379754273159</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.906058082605891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>w_gust_nom</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2497605474849804</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.3704587099451963</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3562471391747686</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.3906103692829024</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.6434219521500937</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.3399684714431901</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.369375711599631</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.3426151452041679</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2276486675160709</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1605048665302865</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.3436444780786522</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7662734775557207</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.57151262297685</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.5987355842826707</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.9069194357226994</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7125890492823992</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1562636309452315</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.1108604409479261</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5450564436133005</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5255722012418892</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.3704587104597201</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.5055568140040309</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.9069194357226993</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3704587104597202</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.2001583147267227</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.2684584026409952</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.1856705090243167</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.1598390494997804</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.02192338176798725</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2027369452535107</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2001583147267227</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.02192338176798721</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.179570802642329</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.1856705090243168</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.1192794499235806</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.2203640874736428</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.8495071615217898</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>w_gust_turn</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.2783353936130029</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.1650657965308676</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.257864282196233</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.6097093867996546</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1871962062795376</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.1541101352642322</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.6853934730624766</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.7294817736314603</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1397306817943849</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.241307113623562</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.1006543162427618</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3352871446537484</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.57151262297685</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.04613571069609571</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.3025192542596155</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4826895367252348</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2475406159088194</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.08375985912209032</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.2300671538071171</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1867647153725482</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.1650657954754105</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.2169282222137577</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3025192542596155</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1650657954754104</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.6688178540588359</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.134132091098594</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.08672385091936062</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.2415069585944543</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.08148433069829711</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.06899591472220637</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.6688178540588359</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.08148433069829748</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.5446538217239776</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.0867238509193605</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.5290218526818218</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.05295014975451765</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.4313584206794568</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>drag_factor</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.004943669007177508</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3278008435688612</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.03501741600656758</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.07384300833206615</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1537295004398183</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.005518282565850646</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.08574665622217023</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.110278360469406</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.4798399653174872</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.5544230703940533</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1433577675608064</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.5465534652308619</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.5987355842826707</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.04613571069609571</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7307366851472981</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.4780672872967964</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.116225681980524</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6068478982731564</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5646082155790292</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.6166623887074741</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3278008438543977</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4970726132935777</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.7307366851472982</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.3278008438543986</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1844704694148171</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.4512550072669436</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.04325634106677755</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.5539996384342424</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.530495460633253</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4589454206137027</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.1844704694148171</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.5304954606332528</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.2797156353721985</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.04325634106677761</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.1263303655451058</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.09059668173209258</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.607547971547399</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_deg</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3020922449780772</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1272848259658045</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.04427991885299578</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.02095703153331036</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4783508849486027</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2321964767408604</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2648599069758623</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1961818237894118</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.3438211252280233</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.2186475821255895</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3363563335652405</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.8355294643232462</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.9069194357226994</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.3025192542596155</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7307366851472981</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.6156564576634754</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2022072857261956</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1363062059009218</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3308713530119787</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.3356589780751157</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1272848271787829</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2745756780239266</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.1272848271787836</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.004293100666281988</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.5723365700339559</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.09228131170171831</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.2178168374086408</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.05683087703562942</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.01431369469022968</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.004293100666281988</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.05683087703562943</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.1820087884363895</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.09228131170171858</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1922076264567233</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.2859818483410696</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.7918129001731299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_a_deg</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.4014455975222316</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.08745563285236241</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3619597769478439</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2777763140759901</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.5163676029087079</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.5117704474277378</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2040537154341386</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.2416274990040327</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2130655323741962</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01904522046582025</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.5919100597908437</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4998057662845655</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.7125890492823992</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4826895367252348</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.4780672872967964</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.6156564576634754</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3732624615896562</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.05414949750249935</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5030184098496708</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4493755621936119</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.08745563219771912</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.3989282463232436</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6156564576634751</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.08745563219771904</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1370954120704695</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.1627306195854173</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.3164652586784148</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.0186218925338228</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.0230958132414128</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.1511927862291947</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.1370954120704695</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.02309581324141264</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.01402347074039929</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.3164652586784147</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.4244111686792689</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.5142487435807532</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.4946531669849729</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_e_deg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.254011483537437</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6298130794149288</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8457736677527872</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8214293357776151</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.474024985832473</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.47599895171627</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.04295484120126973</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.03129633832426991</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2330190229921311</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.08270056165868929</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1921715976841662</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1485648886518352</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.1562636309452315</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.2475406159088194</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.116225681980524</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.2022072857261956</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.3732624615896562</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.02864178843910915</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.7024484160860041</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.6566279232695149</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6298130779985032</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.7060420125610821</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.2022072857261955</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.6298130779985022</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2313689992845301</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.7614552910909091</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.4072752946739412</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.08331037862428302</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.3781075498462348</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.6307169864889388</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.2313689992845301</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.3781075498462349</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.6626938569446458</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.4072752946739404</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.6389620163694368</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.01750398051655414</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.139298734495655</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_r_deg</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.549120350089117</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5127027321388722</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.2587778782229514</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1414807618626842</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01110018623663566</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.3232238354603366</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2810482472316055</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.3095685179641162</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.08006325483782156</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.3515098139712672</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.05385418484894396</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.02305514865496865</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.1108604409479261</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.08375985912209032</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.6068478982731564</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1363062059009218</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.05414949750249935</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.02864178843910915</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5196438065356713</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.5409497523504561</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.5127027322734725</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.5267509873704396</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.136306205900922</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.5127027322734741</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.6327080339170252</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.1159823482007305</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.5519620204170271</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.352220292971236</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.8443697203002418</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.663342164139945</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.6327080339170252</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.8443697203002416</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.0903713968962577</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.5519620204170271</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.3242409425279023</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.1204006133393903</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.2022207597710157</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>nom_sink_rate_mps</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.3949052624839888</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.882012216217645</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6267494588433714</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.693283656233855</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5928765450455016</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.283136973365745</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1623472317239822</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.1435978099186787</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.05736411859110101</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.44176953644817</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2096691688293588</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.2082812032563501</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.5450564436133005</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.2300671538071171</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5646082155790292</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3308713530119787</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.5030184098496708</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7024484160860041</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5196438065356713</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.9915938650304753</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.8820122157506946</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9902053549987263</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.3308713530119788</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.8820122157506946</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.3932684676163655</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.2727039095644468</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.180603142289102</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.442180348969687</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.7539756246184939</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.8980548497462052</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.3932684676163655</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.7539756246184937</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.4504237327219295</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.1806031422891015</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.4790990562549945</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.0249137804446419</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.5514677827187308</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>nom_L_over_D</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.4119425645324213</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.883717634490259</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.6212620326209123</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.6453922249448217</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.5117238453719</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.2510940835239076</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1540553686609466</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1419244534571302</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.03266764245948673</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5028356175743663</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.1513530209804821</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2337601809647161</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5255722012418892</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.1867647153725482</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.6166623887074741</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.3356589780751157</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4493755621936119</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.6566279232695149</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.5409497523504561</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.9915938650304753</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.8837176340315794</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.9813903408587017</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.3356589780751162</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.8837176340315794</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.3907567145483512</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.1989046408957753</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.190757690443688</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.5032173060174254</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.7885839974037078</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.9199291836531722</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.3907567145483512</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.7885839974037078</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-0.4160326188573351</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.1907576904436875</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.3861424631573083</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.07549382286789819</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.5715061472661462</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>nom_CL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.6323336311502682</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5526790592065031</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7644435093594708</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5327457403651186</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0982434699135355</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.1752077084033823</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.18009948675122</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.261241027732491</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.4117798323008935</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.04669495819636894</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.03946968214000521</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.3704587104597201</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.1650657954754105</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3278008438543977</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1272848271787829</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.08745563219771912</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6298130779985032</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5127027322734725</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.8820122157506946</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.8837176340315794</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.938003666846546</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-0.1272848271787831</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.43553623960803</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.2271364684818863</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.001501068264282026</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.4124394135836249</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.7556876362594286</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.901061452541423</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.43553623960803</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.7556876362594287</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.6333934399079918</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.00150106826428257</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.3935886775030049</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.292105351510596</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.4524788241769059</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nom_D</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.4759206927267052</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9380036671794407</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6185130375315685</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7368704817016303</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6052393838982794</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2390584507190955</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1791086307265989</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.1664532322572654</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1400056957961414</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.4311890865821416</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1521424321389192</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.1554086424274072</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5055568140040309</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.2169282222137577</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.4970726132935777</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2745756780239266</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.3989282463232436</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7060420125610821</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.5267509873704396</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9902053549987263</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9813903408587017</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.938003666846546</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.274575678023927</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.9380036668465463</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.4110615793711796</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.2802716226779182</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.1287549589104902</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.4316943078897784</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.7679193157404793</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.916824594732791</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-0.4110615793711796</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.7679193157404794</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.5185610247594037</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.1287549589104897</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.4812923870590251</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.09280774573970435</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.5285123540941312</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_margin_deg</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.3020922449780769</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.1272848259658047</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.04427991885299579</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.02095703153331021</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.4783508849486028</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2321964767408603</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2648599069758623</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1961818237894117</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3438211252280232</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2186475821255896</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.3363563335652404</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8355294643232462</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9069194357226993</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3025192542596155</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.7307366851472982</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6156564576634751</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2022072857261955</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.136306205900922</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3308713530119788</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.3356589780751162</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.1272848271787831</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.274575678023927</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.1272848271787838</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.004293100666282071</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.5723365700339559</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.09228131170171833</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.2178168374086409</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.05683087703562927</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.01431369469022983</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.004293100666282071</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-0.05683087703562922</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.1820087884363895</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-0.09228131170171855</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-0.1922076264567233</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.2859818483410695</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-0.7918129001731299</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>nom_cl_margin_to_cap</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.6323336311502695</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.9999999999999997</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.5526790592065015</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.7644435093594701</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.532745740365118</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.09824346991353594</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1752077084033816</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.18009948675122</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2612410277324909</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4117798323008938</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.04669495819636869</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.03946968214000619</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3704587104597202</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1650657954754104</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3278008438543986</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.1272848271787836</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.08745563219771904</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.6298130779985022</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5127027322734741</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.8820122157506946</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.8837176340315794</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.9380036668465463</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.1272848271787838</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.435536239608031</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.2271364684818856</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.001501068264283202</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.4124394135836243</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.755687636259429</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.9010614525414231</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.435536239608031</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.7556876362594289</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-0.6333934399079924</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.001501068264283754</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.3935886775030046</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.2921053515105956</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-0.4524788241769067</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>turn_alpha_deg</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.3779015287250502</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4355362400081345</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01989204298696813</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5233083812020192</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.05888169437746115</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.06817258998359825</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4481298887563213</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4255507246605898</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.001621764008553666</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.1038248129807936</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.1797033954963047</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.07790797825568674</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.2001583147267227</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.6688178540588359</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1844704694148171</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.004293100666281988</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.1370954120704695</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.2313689992845301</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.6327080339170252</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.3932684676163655</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.3907567145483512</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.43553623960803</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.4110615793711796</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.004293100666282071</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.435536239608031</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.06628121678443293</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.5668743843216978</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.1047525146189572</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.4951434010440465</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.5229248343468282</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.4951434010440461</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.660302481527628</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.5668743843216979</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.5179126137413106</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.2622827820857021</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.2997475598345009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_a_deg</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.01641054682634579</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2271364705916465</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5052754790452935</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5684103682387143</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.2260909506616824</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1442857179695738</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2662839043227594</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.08283774629124388</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4604233646733658</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1225213764440871</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.04161326125097158</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.6542103990553929</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.2684584026409952</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.134132091098594</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.4512550072669436</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.5723365700339559</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.1627306195854173</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.7614552910909091</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.1159823482007305</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.2727039095644468</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.1989046408957753</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2271364684818863</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.2802716226779182</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.5723365700339559</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-0.2271364684818856</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.06628121678443293</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.3047283781122181</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.1221384837954816</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.1631789306119826</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.2701264607947383</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-0.06628121678443319</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.1631789306119822</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.397098188720325</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.3047283781122175</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-0.7731570457988013</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.04423833522603387</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-0.4689697074645675</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_e_deg</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.4915904771389252</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.001501066533709819</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7171658090957048</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1440169393177145</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1440238720479926</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1618611448733983</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.1226408583248415</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.00244471304875248</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.3820983595812321</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.03738081822922935</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2174293059873264</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.104863491325826</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.1856705090243167</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.08672385091936062</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.04325634106677755</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.09228131170171831</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.3164652586784148</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.4072752946739412</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.5519620204170271</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.180603142289102</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-0.190757690443688</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.001501068264282026</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.1287549589104902</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.09228131170171833</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.001501068264283202</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.5668743843216978</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.3047283781122181</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-0.03629343109088035</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>-0.1765922850767352</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.02351304932602678</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.5668743843216978</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.1765922850767354</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-0.195242502965818</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.1111638534454585</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-0.188093218934827</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.0741104779338</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>turn_delta_r_deg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.1469740947035262</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.4124394131182822</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.2398086160001855</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.01601863662038023</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.0621306215879416</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.2639326718185028</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.07514810458635132</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.01403553289964021</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.151521110768691</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.9999983251136108</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5833690735283977</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.05587948899151336</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1598390494997804</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.2415069585944543</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.5539996384342424</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.2178168374086408</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0186218925338228</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.08331037862428302</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.352220292971236</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.442180348969687</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.5032173060174254</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-0.4124394135836249</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.4316943078897784</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.2178168374086409</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.4124394135836243</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-0.1047525146189572</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.1221384837954816</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.03629343109088035</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.503603661164145</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.5487651646411981</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.1047525146189572</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.5036036611641447</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>-0.04255086885871354</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>-0.03629343109088029</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>-0.1567373839721397</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.6710686590725857</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-0.09146403434475138</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>turn_CL</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.6724399739728355</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7556876367965371</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1925054062235446</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3641142814686275</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.07478846560194653</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1595207514416855</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.4132967534265909</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.4059389105538061</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.05633434435437317</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.5027708858715679</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.09081843054350537</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1458277293380356</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.02192338176798725</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.08148433069829711</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.530495460633253</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.05683087703562942</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.0230958132414128</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.3781075498462348</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.8443697203002418</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.7539756246184939</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-0.7885839974037078</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.7556876362594286</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.7679193157404793</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.05683087703562927</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.755687636259429</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.4951434010440465</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.1631789306119826</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-0.1765922850767352</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.503603661164145</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.9257512200133612</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.495143401044046</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.248892022186675</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-0.1765922850767354</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>-0.3374356069750512</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.2346308200112265</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.1788833400343645</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>turn_D</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.6424114596003598</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9010614530522529</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4949718415819724</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6145499840364886</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2822156962284013</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1311229802519437</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.2192296709863068</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.2051086158353365</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.07909825055794842</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.5479155075413978</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.08753317148258534</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.04358614016321346</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.2027369452535107</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.06899591472220637</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.4589454206137027</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.01431369469022968</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.1511927862291947</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.6307169864889388</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.663342164139945</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.8980548497462052</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-0.9199291836531722</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.901061452541423</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.916824594732791</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.01431369469022983</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.9010614525414231</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5229248343468282</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2701264607947383</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.02351304932602678</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.5487651646411981</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.9257512200133612</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.5229248343468283</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-0.9257512200133612</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.5082077272067073</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.02351304932602711</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.4056175461776309</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.2983935069011512</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.3332314719711805</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>turn_alpha_margin_deg</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.3779015287250502</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.4355362400081345</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.01989204298696813</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.5233083812020192</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.05888169437746115</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.06817258998359825</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.4481298887563213</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.4255507246605898</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.001621764008553666</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.1038248129807936</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1797033954963047</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.07790797825568674</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2001583147267227</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.6688178540588359</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.1844704694148171</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.004293100666281988</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1370954120704695</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-0.2313689992845301</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-0.6327080339170252</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.3932684676163655</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.3907567145483512</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-0.43553623960803</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-0.4110615793711796</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.004293100666282071</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.435536239608031</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.06628121678443319</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.5668743843216978</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.1047525146189572</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-0.495143401044046</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.5229248343468283</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.4951434010440461</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.660302481527628</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.5668743843216979</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.5179126137413106</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-0.2622827820857021</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.2997475598345009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>turn_cl_margin_to_cap</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.6724399739728358</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.7556876367965372</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.1925054062235445</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.3641142814686273</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.07478846560194674</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1595207514416852</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4132967534265911</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4059389105538065</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.05633434435437332</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.5027708858715675</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.09081843054350495</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.1458277293380352</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.02192338176798721</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.08148433069829748</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.5304954606332528</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.05683087703562943</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.02309581324141264</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.3781075498462349</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.8443697203002416</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.7539756246184937</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.7885839974037078</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.7556876362594287</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.7679193157404794</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-0.05683087703562922</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.7556876362594289</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.4951434010440461</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.1631789306119822</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.1765922850767354</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.5036036611641447</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-0.9257512200133612</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.4951434010440461</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>-0.2488920221866751</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.1765922850767356</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.3374356069750514</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>-0.2346308200112261</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-0.1788833400343648</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_a</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.4382743889083938</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6333934400563377</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5062053789809247</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8547901357398259</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.324268616015381</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.3986392115562608</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4277450841542153</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4215511243353974</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.338497707195412</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.04155317726218683</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.19237994105271</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0602603957490512</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.179570802642329</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-0.5446538217239776</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-0.2797156353721985</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.1820087884363895</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.01402347074039929</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.6626938569446458</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.0903713968962577</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.4504237327219295</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-0.4160326188573351</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.6333934399079918</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.5185610247594037</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.1820087884363895</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-0.6333934399079924</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.660302481527628</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.397098188720325</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.195242502965818</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-0.04255086885871354</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.248892022186675</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.5082077272067073</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-0.660302481527628</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-0.2488920221866751</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-0.1952425029658184</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.5285648073366356</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.3804586670194766</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.2449522609174804</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_e</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.4915904771389256</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.001501066533710352</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.7171658090957043</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.144016939317714</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1440238720479921</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1618611448733981</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.1226408583248411</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.002444713048752145</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.3820983595812325</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.03738081822922917</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2174293059873263</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.1048634913258264</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.1856705090243168</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.0867238509193605</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.04325634106677761</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.09228131170171858</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.3164652586784147</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.4072752946739404</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-0.5519620204170271</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.1806031422891015</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-0.1907576904436875</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.00150106826428257</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.1287549589104897</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-0.09228131170171855</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.001501068264283754</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-0.5668743843216979</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.3047283781122175</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.03629343109088029</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-0.1765922850767354</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-0.02351304932602711</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.5668743843216979</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.1765922850767356</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-0.1952425029658184</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.111163853445459</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-0.1880932189348272</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.0741104779338003</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>turn_util_r</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.117496327546919</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.3935886789888393</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.2802059847529678</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.7016566579253276</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.417500246311398</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.10370030232325</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.08509743124589217</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.0369371518225427</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.5002206080030146</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.1573063403644544</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.2030496439843069</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.348003792600847</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1192794499235806</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5290218526818218</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.1263303655451058</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.1922076264567233</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.4244111686792689</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.6389620163694368</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-0.3242409425279023</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.4790990562549945</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.3861424631573083</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.3935886775030049</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.4812923870590251</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.1922076264567233</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.3935886775030046</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.5179126137413106</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.7731570457988013</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.1111638534454585</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.1567373839721397</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-0.3374356069750512</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-0.4056175461776309</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.5179126137413106</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.3374356069750514</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.5285648073366356</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.111163853445459</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.08748208669706593</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.1032563355606751</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>turn_wing_deflection_proxy_over_allow</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.1984590605862184</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.2921053514105905</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1373403271209359</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1676496820101165</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.2220347781533375</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01792155693698842</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1580938818146259</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2754061300662249</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.08701071515137776</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.6708344977861006</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.963451109993147</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.4314379754273159</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.2203640874736428</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.05295014975451765</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.09059668173209258</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-0.2859818483410696</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.5142487435807532</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.01750398051655414</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.1204006133393903</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.0249137804446419</v>
+      </c>
+      <c r="V38" t="n">
+        <v>-0.07549382286789819</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.292105351510596</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.09280774573970435</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.2859818483410695</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.2921053515105956</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.2622827820857021</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.04423833522603387</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-0.188093218934827</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-0.6710686590725857</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.2346308200112265</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.2983935069011512</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-0.2622827820857021</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-0.2346308200112261</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.3804586670194766</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>-0.1880932189348272</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.08748208669706593</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-0.262769297579063</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>turn_htail_deflection_proxy_over_allow</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.1001398054301394</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.452478823289782</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.3104835129623918</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3318118594167773</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.4234702396020608</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2934574525642376</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3992166788083074</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2485042607621609</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.3811136755856935</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.09159666937122866</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3964912550450069</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.906058082605891</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-0.8495071615217898</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.4313584206794568</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.607547971547399</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.7918129001731299</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.4946531669849729</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.139298734495655</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.2022207597710157</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.5514677827187308</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-0.5715061472661462</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.4524788241769059</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.5285123540941312</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-0.7918129001731299</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.4524788241769067</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.2997475598345009</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.4689697074645675</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.0741104779338</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.09146403434475138</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.1788833400343645</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.3332314719711805</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-0.2997475598345009</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-0.1788833400343648</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.2449522609174804</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.0741104779338003</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.1032563355606751</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-0.262769297579063</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10494,7 +18060,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60dcbd7</t>
+          <t>7228918-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/02_Glider_Design/C_results/nausicaa_workflow.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_workflow.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>becd544-dirty</t>
+          <t>65ef22b-dirty</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-12T14:23:18.452935+00:00</t>
+          <t>2026-04-13T22:48:27.432809+00:00</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>becd544-dirty</t>
+          <t>65ef22b-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11601,7 +11601,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.3080000000000001</v>
+        <v>0.4770000000000002</v>
       </c>
     </row>
     <row r="159">
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.6020000000000002</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="160">
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6970000000000002</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="162">
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7.460999999999999</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="163">
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2.568</v>
+        <v>3.974</v>
       </c>
     </row>
     <row r="164">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>11.659</v>
+        <v>17.849</v>
       </c>
     </row>
     <row r="165">
@@ -11681,7 +11681,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.3095909999999999</v>
+        <v>0.4823419999999999</v>
       </c>
     </row>
     <row r="167">
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.59902</v>
+        <v>1.004327</v>
       </c>
     </row>
     <row r="168">
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.697962</v>
+        <v>1.079192</v>
       </c>
     </row>
     <row r="170">
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7.460197000000001</v>
+        <v>11.269779</v>
       </c>
     </row>
     <row r="171">
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2.564164</v>
+        <v>3.97445</v>
       </c>
     </row>
     <row r="172">
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>11.658973</v>
+        <v>17.848511</v>
       </c>
     </row>
     <row r="173">
